--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Microschool_With_Decisions.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Microschool_With_Decisions.xlsx
@@ -27,14 +27,15 @@
     <sheet sheetId="21" name="Underwriting Snapshot" state="visible" r:id="rId24"/>
     <sheet sheetId="22" name="Financial Health" state="visible" r:id="rId25"/>
     <sheet sheetId="23" name="Budget Narrative" state="visible" r:id="rId26"/>
-    <sheet sheetId="24" name="Decision History" state="visible" r:id="rId27"/>
+    <sheet sheetId="24" name="Assumptions Memo" state="visible" r:id="rId27"/>
+    <sheet sheetId="25" name="Decision History" state="visible" r:id="rId28"/>
   </sheets>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="835" uniqueCount="479">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="838" uniqueCount="482">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -42,7 +43,7 @@
     <t>Bright Horizons Microschool</t>
   </si>
   <si>
-    <t>Generated April 29, 2026 · llc_single</t>
+    <t>Generated May 1, 2026 · llc_single</t>
   </si>
   <si>
     <t>Cell Color Legend</t>
@@ -162,7 +163,7 @@
     <t>Model Date</t>
   </si>
   <si>
-    <t>April 29, 2026</t>
+    <t>May 1, 2026</t>
   </si>
   <si>
     <t>Stage</t>
@@ -1167,7 +1168,7 @@
     <t>Bright Horizons Microschool — Financial Health Dashboard</t>
   </si>
   <si>
-    <t>Generated April 29, 2026</t>
+    <t>Generated May 1, 2026</t>
   </si>
   <si>
     <t>● Green = healthy</t>
@@ -1357,6 +1358,15 @@
   </si>
   <si>
     <t>Additional Context</t>
+  </si>
+  <si>
+    <t>Assumptions Memo</t>
+  </si>
+  <si>
+    <t>Founder-supplied reasoning for each assumption captured during the wizard. Empty when no rationale was entered for that area.</t>
+  </si>
+  <si>
+    <t>No founder rationale captured.</t>
   </si>
   <si>
     <t>Decision History</t>
@@ -1493,7 +1503,7 @@
     <numFmt numFmtId="167" formatCode="0.0"/>
     <numFmt numFmtId="168" formatCode="0.00x"/>
   </numFmts>
-  <fonts count="27" x14ac:knownFonts="1">
+  <fonts count="28" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1651,6 +1661,11 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -1751,7 +1766,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="93">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1892,6 +1907,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -7708,6 +7727,54 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="32" customWidth="1"/>
+    <col min="2" max="2" width="38" customWidth="1"/>
+    <col min="3" max="3" width="70" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="21" t="s">
+        <v>441</v>
+      </c>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="82" t="s">
+        <v>442</v>
+      </c>
+      <c r="B2" s="82"/>
+      <c r="C2" s="82"/>
+    </row>
+    <row r="4" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="83" t="s">
+        <v>443</v>
+      </c>
+      <c r="B4" s="83"/>
+      <c r="C4" s="83"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A4:C4"/>
+  </mergeCells>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddFooter>&amp;L&amp;8SchoolStack Budget&amp;C&amp;8Confidential&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -7726,7 +7793,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B1" s="15" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="C1" s="15"/>
       <c r="D1" s="15"/>
@@ -7736,162 +7803,162 @@
       <c r="H1" s="15"/>
     </row>
     <row r="2" ht="44" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="82" t="s">
-        <v>442</v>
-      </c>
-      <c r="C2" s="82"/>
-      <c r="D2" s="82"/>
-      <c r="E2" s="82"/>
-      <c r="F2" s="82"/>
-      <c r="G2" s="82"/>
-      <c r="H2" s="82"/>
+      <c r="B2" s="84" t="s">
+        <v>445</v>
+      </c>
+      <c r="C2" s="84"/>
+      <c r="D2" s="84"/>
+      <c r="E2" s="84"/>
+      <c r="F2" s="84"/>
+      <c r="G2" s="84"/>
+      <c r="H2" s="84"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B4" s="83" t="s">
-        <v>443</v>
-      </c>
-      <c r="C4" s="83" t="s">
+      <c r="B4" s="85" t="s">
+        <v>446</v>
+      </c>
+      <c r="C4" s="85" t="s">
         <v>132</v>
       </c>
-      <c r="D4" s="83" t="s">
-        <v>444</v>
-      </c>
-      <c r="E4" s="83" t="s">
-        <v>445</v>
-      </c>
-      <c r="F4" s="83" t="s">
-        <v>446</v>
-      </c>
-      <c r="G4" s="83" t="s">
+      <c r="D4" s="85" t="s">
         <v>447</v>
       </c>
-      <c r="H4" s="83" t="s">
+      <c r="E4" s="85" t="s">
         <v>448</v>
       </c>
+      <c r="F4" s="85" t="s">
+        <v>449</v>
+      </c>
+      <c r="G4" s="85" t="s">
+        <v>450</v>
+      </c>
+      <c r="H4" s="85" t="s">
+        <v>451</v>
+      </c>
     </row>
     <row r="5" ht="64" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="84"/>
-      <c r="B5" s="85" t="s">
-        <v>449</v>
-      </c>
-      <c r="C5" s="86" t="s">
-        <v>450</v>
-      </c>
-      <c r="D5" s="87" t="s">
-        <v>451</v>
-      </c>
-      <c r="E5" s="86" t="s">
+      <c r="A5" s="86"/>
+      <c r="B5" s="87" t="s">
         <v>452</v>
       </c>
-      <c r="F5" s="88" t="s">
+      <c r="C5" s="88" t="s">
         <v>453</v>
       </c>
-      <c r="G5" s="86" t="s">
+      <c r="D5" s="89" t="s">
         <v>454</v>
       </c>
-      <c r="H5" s="86" t="s">
+      <c r="E5" s="88" t="s">
         <v>455</v>
       </c>
+      <c r="F5" s="90" t="s">
+        <v>456</v>
+      </c>
+      <c r="G5" s="88" t="s">
+        <v>457</v>
+      </c>
+      <c r="H5" s="88" t="s">
+        <v>458</v>
+      </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="84"/>
-      <c r="B6" s="85" t="s">
-        <v>456</v>
-      </c>
-      <c r="C6" s="86" t="s">
-        <v>457</v>
-      </c>
-      <c r="D6" s="87" t="s">
-        <v>451</v>
-      </c>
-      <c r="E6" s="86" t="s">
-        <v>458</v>
-      </c>
-      <c r="F6" s="88" t="s">
+      <c r="A6" s="86"/>
+      <c r="B6" s="87" t="s">
         <v>459</v>
       </c>
-      <c r="G6" s="86" t="s">
+      <c r="C6" s="88" t="s">
         <v>460</v>
       </c>
-      <c r="H6" s="86" t="s">
+      <c r="D6" s="89" t="s">
+        <v>454</v>
+      </c>
+      <c r="E6" s="88" t="s">
         <v>461</v>
       </c>
+      <c r="F6" s="90" t="s">
+        <v>462</v>
+      </c>
+      <c r="G6" s="88" t="s">
+        <v>463</v>
+      </c>
+      <c r="H6" s="88" t="s">
+        <v>464</v>
+      </c>
     </row>
     <row r="7" ht="64" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="89"/>
-      <c r="B7" s="85" t="s">
-        <v>462</v>
-      </c>
-      <c r="C7" s="86" t="s">
-        <v>463</v>
-      </c>
-      <c r="D7" s="90" t="s">
-        <v>464</v>
-      </c>
-      <c r="E7" s="86" t="s">
+      <c r="A7" s="91"/>
+      <c r="B7" s="87" t="s">
         <v>465</v>
       </c>
-      <c r="F7" s="88" t="s">
+      <c r="C7" s="88" t="s">
         <v>466</v>
       </c>
-      <c r="G7" s="86" t="s">
+      <c r="D7" s="92" t="s">
         <v>467</v>
       </c>
-      <c r="H7" s="86" t="s">
+      <c r="E7" s="88" t="s">
         <v>468</v>
       </c>
+      <c r="F7" s="90" t="s">
+        <v>469</v>
+      </c>
+      <c r="G7" s="88" t="s">
+        <v>470</v>
+      </c>
+      <c r="H7" s="88" t="s">
+        <v>471</v>
+      </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="91"/>
-      <c r="B8" s="85" t="s">
-        <v>469</v>
-      </c>
-      <c r="C8" s="86" t="s">
-        <v>457</v>
-      </c>
-      <c r="D8" s="92" t="s">
-        <v>470</v>
-      </c>
-      <c r="E8" s="86" t="s">
-        <v>465</v>
-      </c>
-      <c r="F8" s="88" t="s">
-        <v>471</v>
-      </c>
-      <c r="G8" s="86" t="s">
+      <c r="A8" s="93"/>
+      <c r="B8" s="87" t="s">
         <v>472</v>
       </c>
-      <c r="H8" s="86" t="s">
+      <c r="C8" s="88" t="s">
+        <v>460</v>
+      </c>
+      <c r="D8" s="94" t="s">
         <v>473</v>
       </c>
+      <c r="E8" s="88" t="s">
+        <v>468</v>
+      </c>
+      <c r="F8" s="90" t="s">
+        <v>474</v>
+      </c>
+      <c r="G8" s="88" t="s">
+        <v>475</v>
+      </c>
+      <c r="H8" s="88" t="s">
+        <v>476</v>
+      </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="91"/>
-      <c r="B9" s="85" t="s">
-        <v>474</v>
-      </c>
-      <c r="C9" s="86" t="s">
-        <v>463</v>
-      </c>
-      <c r="D9" s="92" t="s">
-        <v>470</v>
-      </c>
-      <c r="E9" s="86" t="s">
-        <v>465</v>
-      </c>
-      <c r="F9" s="88" t="s">
-        <v>475</v>
-      </c>
-      <c r="G9" s="86" t="s">
-        <v>476</v>
-      </c>
-      <c r="H9" s="86" t="s">
+      <c r="A9" s="93"/>
+      <c r="B9" s="87" t="s">
         <v>477</v>
+      </c>
+      <c r="C9" s="88" t="s">
+        <v>466</v>
+      </c>
+      <c r="D9" s="94" t="s">
+        <v>473</v>
+      </c>
+      <c r="E9" s="88" t="s">
+        <v>468</v>
+      </c>
+      <c r="F9" s="90" t="s">
+        <v>478</v>
+      </c>
+      <c r="G9" s="88" t="s">
+        <v>479</v>
+      </c>
+      <c r="H9" s="88" t="s">
+        <v>480</v>
       </c>
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B11" s="58" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="C11" s="58"/>
       <c r="D11" s="58"/>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Microschool_With_Decisions.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Microschool_With_Decisions.xlsx
@@ -43,7 +43,7 @@
     <t>Bright Horizons Microschool</t>
   </si>
   <si>
-    <t>Generated May 1, 2026 · llc_single</t>
+    <t>Generated May 7, 2026 · llc_single</t>
   </si>
   <si>
     <t>Cell Color Legend</t>
@@ -163,7 +163,7 @@
     <t>Model Date</t>
   </si>
   <si>
-    <t>May 1, 2026</t>
+    <t>May 7, 2026</t>
   </si>
   <si>
     <t>Stage</t>
@@ -1168,7 +1168,7 @@
     <t>Bright Horizons Microschool — Financial Health Dashboard</t>
   </si>
   <si>
-    <t>Generated May 1, 2026</t>
+    <t>Generated May 7, 2026</t>
   </si>
   <si>
     <t>● Green = healthy</t>
@@ -1273,7 +1273,7 @@
     <t>The model reaches profit early and sustains strong margins through Year 5.</t>
   </si>
   <si>
-    <t>Monitor enrollment actuals vs. projections in Year 1.</t>
+    <t>Compare your real Year 1 enrollment against this projection as students enroll.</t>
   </si>
   <si>
     <t>Liquidity</t>
@@ -1288,7 +1288,7 @@
     <t>Staffing Burden</t>
   </si>
   <si>
-    <t>Staffing at 32% of revenue leaves room for facilities, programs, and reserves.</t>
+    <t>Staffing at 31% of revenue leaves room for facilities, programs, and reserves.</t>
   </si>
   <si>
     <t>As you add staff, ensure staffing stays below 60% of revenue.</t>
@@ -1315,7 +1315,7 @@
     <t>Reserve Strength</t>
   </si>
   <si>
-    <t>51.3 months of reserves by Year 5 — a strong buffer for unexpected costs.</t>
+    <t>52.1 months of reserves by Year 5 — a strong buffer for unexpected costs.</t>
   </si>
   <si>
     <t>Continue growing reserves toward 6 months for best-in-class financial health.</t>
@@ -1470,7 +1470,7 @@
   </si>
   <si>
     <t xml:space="preserve">• Enrollment -8 cumulative
-• Tuition $-500/student</t>
+• Tuition -$500/student</t>
   </si>
   <si>
     <t>Board declined; enrollment goals retained as originally modeled.</t>
@@ -3220,19 +3220,19 @@
       </c>
       <c r="C10" s="31">
         <f>SUM(C5:C9)</f>
-        <v>339130</v>
+        <v>340512</v>
       </c>
       <c r="D10" s="31">
         <f>SUM(D5:D9)</f>
-        <v>424882</v>
+        <v>427946</v>
       </c>
       <c r="E10" s="31">
         <f>SUM(E5:E9)</f>
-        <v>495517</v>
+        <v>500518</v>
       </c>
       <c r="F10" s="31">
         <f>SUM(F5:F9)</f>
-        <v>509276</v>
+        <v>516085</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3629,19 +3629,19 @@
       </c>
       <c r="C4" s="33">
         <f>'Budget Detail'!C10</f>
-        <v>339130</v>
+        <v>340512</v>
       </c>
       <c r="D4" s="33">
         <f>'Budget Detail'!D10</f>
-        <v>424882</v>
+        <v>427946</v>
       </c>
       <c r="E4" s="33">
         <f>'Budget Detail'!E10</f>
-        <v>495517</v>
+        <v>500518</v>
       </c>
       <c r="F4" s="33">
         <f>'Budget Detail'!F10</f>
-        <v>509276</v>
+        <v>516085</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -3760,23 +3760,23 @@
       </c>
       <c r="B11" s="32">
         <f>B4-B8</f>
-        <v>25233</v>
+        <v>25232</v>
       </c>
       <c r="C11" s="32">
         <f>C4-C8</f>
-        <v>137125</v>
+        <v>138507</v>
       </c>
       <c r="D11" s="32">
         <f>D4-D8</f>
-        <v>213423</v>
+        <v>216486</v>
       </c>
       <c r="E11" s="32">
         <f>E4-E8</f>
-        <v>275091</v>
+        <v>280092</v>
       </c>
       <c r="F11" s="32">
         <f>F4-F8</f>
-        <v>282237</v>
+        <v>289046</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -3789,19 +3789,19 @@
       </c>
       <c r="C12" s="29">
         <f>IF(C4=0,0,C11/C4)</f>
-        <v>0.40434379</v>
+        <v>0.40676208</v>
       </c>
       <c r="D12" s="29">
         <f>IF(D4=0,0,D11/D4)</f>
-        <v>0.50230996</v>
+        <v>0.50587283</v>
       </c>
       <c r="E12" s="29">
         <f>IF(E4=0,0,E11/E4)</f>
-        <v>0.55515954</v>
+        <v>0.55960384</v>
       </c>
       <c r="F12" s="29">
         <f>IF(F4=0,0,F11/F4)</f>
-        <v>0.5541927</v>
+        <v>0.56007487</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -3809,19 +3809,19 @@
         <v>275</v>
       </c>
       <c r="B13" s="30">
-        <v>25233</v>
+        <v>25232</v>
       </c>
       <c r="C13" s="30">
-        <v>162357</v>
+        <v>163740</v>
       </c>
       <c r="D13" s="30">
-        <v>375780</v>
+        <v>380226</v>
       </c>
       <c r="E13" s="30">
-        <v>650871</v>
+        <v>660318</v>
       </c>
       <c r="F13" s="30">
-        <v>933108</v>
+        <v>949364</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -3832,16 +3832,16 @@
         <v>15389</v>
       </c>
       <c r="C14" s="30">
-        <v>18841</v>
+        <v>18917</v>
       </c>
       <c r="D14" s="30">
-        <v>19313</v>
+        <v>19452</v>
       </c>
       <c r="E14" s="30">
-        <v>19821</v>
+        <v>20021</v>
       </c>
       <c r="F14" s="30">
-        <v>20371</v>
+        <v>20643</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -4495,16 +4495,16 @@
         <v>184667</v>
       </c>
       <c r="C5" s="31">
-        <v>339130</v>
+        <v>340512</v>
       </c>
       <c r="D5" s="31">
-        <v>424882</v>
+        <v>427946</v>
       </c>
       <c r="E5" s="31">
-        <v>495517</v>
+        <v>500518</v>
       </c>
       <c r="F5" s="31">
-        <v>509276</v>
+        <v>516085</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4642,19 +4642,19 @@
       </c>
       <c r="C15" s="32">
         <f>C5-C12</f>
-        <v>136411</v>
+        <v>137793</v>
       </c>
       <c r="D15" s="32">
         <f>D5-D12</f>
-        <v>212708</v>
+        <v>215772</v>
       </c>
       <c r="E15" s="32">
         <f>E5-E12</f>
-        <v>274377</v>
+        <v>279377</v>
       </c>
       <c r="F15" s="32">
         <f>F5-F12</f>
-        <v>281523</v>
+        <v>288332</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -4667,19 +4667,19 @@
       </c>
       <c r="C16" s="29">
         <f>IF(C5=0,0,C15/C5)</f>
-        <v>0.40223755</v>
+        <v>0.4046644</v>
       </c>
       <c r="D16" s="29">
         <f>IF(D5=0,0,D15/D5)</f>
-        <v>0.50062882</v>
+        <v>0.50420372</v>
       </c>
       <c r="E16" s="29">
         <f>IF(E5=0,0,E15/E5)</f>
-        <v>0.55371804</v>
+        <v>0.55817675</v>
       </c>
       <c r="F16" s="29">
         <f>IF(F5=0,0,F15/F5)</f>
-        <v>0.55279014</v>
+        <v>0.55869082</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -4692,19 +4692,19 @@
       </c>
       <c r="C17" s="33">
         <f>B17+C15</f>
-        <v>160929</v>
+        <v>162311</v>
       </c>
       <c r="D17" s="33">
         <f>C17+D15</f>
-        <v>373637</v>
+        <v>378083</v>
       </c>
       <c r="E17" s="33">
         <f>D17+E15</f>
-        <v>648014</v>
+        <v>657460</v>
       </c>
       <c r="F17" s="33">
         <f>E17+F15</f>
-        <v>929536</v>
+        <v>945792</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -4883,19 +4883,19 @@
       </c>
       <c r="C5" s="47">
         <f>B5+'5-Year Operating Stmt'!C15</f>
-        <v>199295</v>
+        <v>200677</v>
       </c>
       <c r="D5" s="47">
         <f>B5+'5-Year Operating Stmt'!C15+'5-Year Operating Stmt'!D15</f>
-        <v>412717</v>
+        <v>417164</v>
       </c>
       <c r="E5" s="47">
         <f>B5+'5-Year Operating Stmt'!C15+'5-Year Operating Stmt'!D15+'5-Year Operating Stmt'!E15</f>
-        <v>687808</v>
+        <v>697255</v>
       </c>
       <c r="F5" s="47">
         <f>B5+'5-Year Operating Stmt'!C15+'5-Year Operating Stmt'!D15+'5-Year Operating Stmt'!E15+'5-Year Operating Stmt'!F15</f>
-        <v>970045</v>
+        <v>986301</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -4968,19 +4968,19 @@
       </c>
       <c r="C9" s="31">
         <f>SUM(C5:C8)</f>
-        <v>203903</v>
+        <v>205285</v>
       </c>
       <c r="D9" s="31">
         <f>SUM(D5:D8)</f>
-        <v>416642</v>
+        <v>421088</v>
       </c>
       <c r="E9" s="31">
         <f>SUM(E5:E8)</f>
-        <v>691050</v>
+        <v>700496</v>
       </c>
       <c r="F9" s="31">
         <f>SUM(F5:F8)</f>
-        <v>972604</v>
+        <v>988860</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5078,19 +5078,19 @@
       </c>
       <c r="C17" s="32">
         <f>C9-C14</f>
-        <v>203903</v>
+        <v>205285</v>
       </c>
       <c r="D17" s="32">
         <f>D9-D14</f>
-        <v>416642</v>
+        <v>421088</v>
       </c>
       <c r="E17" s="32">
         <f>E9-E14</f>
-        <v>691050</v>
+        <v>700496</v>
       </c>
       <c r="F17" s="32">
         <f>F9-F14</f>
-        <v>972604</v>
+        <v>988860</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -5190,16 +5190,16 @@
         <v>184667</v>
       </c>
       <c r="C5" s="30">
-        <v>339130</v>
+        <v>340512</v>
       </c>
       <c r="D5" s="30">
-        <v>424882</v>
+        <v>427946</v>
       </c>
       <c r="E5" s="30">
-        <v>495517</v>
+        <v>500518</v>
       </c>
       <c r="F5" s="30">
-        <v>509276</v>
+        <v>516085</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -5247,19 +5247,19 @@
         <v>273</v>
       </c>
       <c r="B8" s="33">
-        <v>25233</v>
+        <v>25232</v>
       </c>
       <c r="C8" s="33">
-        <v>137125</v>
+        <v>138507</v>
       </c>
       <c r="D8" s="33">
-        <v>213423</v>
+        <v>216486</v>
       </c>
       <c r="E8" s="33">
-        <v>275091</v>
+        <v>280092</v>
       </c>
       <c r="F8" s="33">
-        <v>282237</v>
+        <v>289046</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -5312,19 +5312,19 @@
       </c>
       <c r="C11" s="33">
         <f>C8+C9+C10</f>
-        <v>137839</v>
+        <v>139222</v>
       </c>
       <c r="D11" s="33">
         <f>D8+D9+D10</f>
-        <v>214137</v>
+        <v>217200</v>
       </c>
       <c r="E11" s="33">
         <f>E8+E9+E10</f>
-        <v>275805</v>
+        <v>280806</v>
       </c>
       <c r="F11" s="33">
         <f>F8+F9+F10</f>
-        <v>282951</v>
+        <v>289761</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -5365,16 +5365,16 @@
         <v>62170</v>
       </c>
       <c r="C15" s="30">
-        <v>199295</v>
+        <v>200677</v>
       </c>
       <c r="D15" s="30">
-        <v>412717</v>
+        <v>417164</v>
       </c>
       <c r="E15" s="30">
-        <v>687808</v>
+        <v>697255</v>
       </c>
       <c r="F15" s="30">
-        <v>970045</v>
+        <v>986301</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -5387,19 +5387,19 @@
       </c>
       <c r="C16" s="50">
         <f>IF((C5-C8)=0,0,(C15/(C5-C8))*365)</f>
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="D16" s="50">
         <f>IF((D5-D8)=0,0,(D15/(D5-D8))*365)</f>
-        <v>712</v>
+        <v>720</v>
       </c>
       <c r="E16" s="50">
         <f>IF((E5-E8)=0,0,(E15/(E5-E8))*365)</f>
-        <v>1139</v>
+        <v>1155</v>
       </c>
       <c r="F16" s="50">
         <f>IF((F5-F8)=0,0,(F15/(F5-F8))*365)</f>
-        <v>1559</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -5412,19 +5412,19 @@
       </c>
       <c r="C17" s="34">
         <f>IF((C5-C8)=0,0,C15/((C5-C8)/12))</f>
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="D17" s="34">
         <f>IF((D5-D8)=0,0,D15/((D5-D8)/12))</f>
-        <v>23.4</v>
+        <v>23.7</v>
       </c>
       <c r="E17" s="34">
         <f>IF((E5-E8)=0,0,E15/((E5-E8)/12))</f>
-        <v>37.4</v>
+        <v>38</v>
       </c>
       <c r="F17" s="34">
         <f>IF((F5-F8)=0,0,F15/((F5-F8)/12))</f>
-        <v>51.3</v>
+        <v>52.1</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -5465,16 +5465,16 @@
         <v>15389</v>
       </c>
       <c r="C21" s="30">
-        <v>18841</v>
+        <v>18917</v>
       </c>
       <c r="D21" s="30">
-        <v>19313</v>
+        <v>19452</v>
       </c>
       <c r="E21" s="30">
-        <v>19821</v>
+        <v>20021</v>
       </c>
       <c r="F21" s="30">
-        <v>20371</v>
+        <v>20643</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -5531,10 +5531,10 @@
         <v>10</v>
       </c>
       <c r="E24" s="51">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F24" s="51">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6163,16 +6163,16 @@
         <v>184667</v>
       </c>
       <c r="C6" s="30">
-        <v>339130</v>
+        <v>340512</v>
       </c>
       <c r="D6" s="30">
-        <v>424882</v>
+        <v>427946</v>
       </c>
       <c r="E6" s="30">
-        <v>495517</v>
+        <v>500518</v>
       </c>
       <c r="F6" s="30">
-        <v>509276</v>
+        <v>516085</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -6200,19 +6200,19 @@
         <v>273</v>
       </c>
       <c r="B8" s="32">
-        <v>25233</v>
+        <v>25232</v>
       </c>
       <c r="C8" s="32">
-        <v>137125</v>
+        <v>138507</v>
       </c>
       <c r="D8" s="32">
-        <v>213423</v>
+        <v>216486</v>
       </c>
       <c r="E8" s="32">
-        <v>275091</v>
+        <v>280092</v>
       </c>
       <c r="F8" s="32">
-        <v>282237</v>
+        <v>289046</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -6220,19 +6220,19 @@
         <v>274</v>
       </c>
       <c r="B9" s="29">
-        <v>0.13663808664259927</v>
+        <v>0.13663808664259913</v>
       </c>
       <c r="C9" s="29">
-        <v>0.4043437853073026</v>
+        <v>0.4067620818062212</v>
       </c>
       <c r="D9" s="29">
-        <v>0.5023099573664649</v>
+        <v>0.5058728257176494</v>
       </c>
       <c r="E9" s="29">
-        <v>0.5551595361077036</v>
+        <v>0.5596038436877832</v>
       </c>
       <c r="F9" s="29">
-        <v>0.5541926962730911</v>
+        <v>0.5600748662293807</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -6269,10 +6269,10 @@
         <v>10</v>
       </c>
       <c r="E11" s="50">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F11" s="50">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6318,16 +6318,16 @@
         <v>147733</v>
       </c>
       <c r="C16" s="30">
-        <v>271304</v>
+        <v>272410</v>
       </c>
       <c r="D16" s="30">
-        <v>339906</v>
+        <v>342357</v>
       </c>
       <c r="E16" s="30">
-        <v>396414</v>
+        <v>400414</v>
       </c>
       <c r="F16" s="30">
-        <v>407420</v>
+        <v>412868</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -6358,16 +6358,16 @@
         <v>-11701</v>
       </c>
       <c r="C18" s="32">
-        <v>69299</v>
+        <v>70405</v>
       </c>
       <c r="D18" s="32">
-        <v>128446</v>
+        <v>130897</v>
       </c>
       <c r="E18" s="32">
-        <v>175988</v>
+        <v>179988</v>
       </c>
       <c r="F18" s="32">
-        <v>180382</v>
+        <v>185829</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -6378,16 +6378,16 @@
         <v>-0.07920239169675096</v>
       </c>
       <c r="C19" s="29">
-        <v>0.2554297316341282</v>
+        <v>0.2584526022577766</v>
       </c>
       <c r="D19" s="29">
-        <v>0.3778874467080811</v>
+        <v>0.3823410321470617</v>
       </c>
       <c r="E19" s="29">
-        <v>0.4439494201346296</v>
+        <v>0.4495048046097289</v>
       </c>
       <c r="F19" s="29">
-        <v>0.44274087034136395</v>
+        <v>0.45009358278672595</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -6568,16 +6568,16 @@
         <v>184667</v>
       </c>
       <c r="E13" s="30">
-        <v>339130</v>
+        <v>340512</v>
       </c>
       <c r="F13" s="30">
-        <v>424882</v>
+        <v>427946</v>
       </c>
       <c r="G13" s="30">
-        <v>495517</v>
+        <v>500518</v>
       </c>
       <c r="H13" s="30">
-        <v>509276</v>
+        <v>516085</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -6605,19 +6605,19 @@
         <v>273</v>
       </c>
       <c r="D15" s="30">
-        <v>25233</v>
+        <v>25232</v>
       </c>
       <c r="E15" s="30">
-        <v>137125</v>
+        <v>138507</v>
       </c>
       <c r="F15" s="30">
-        <v>213423</v>
+        <v>216486</v>
       </c>
       <c r="G15" s="30">
-        <v>275091</v>
+        <v>280092</v>
       </c>
       <c r="H15" s="30">
-        <v>282237</v>
+        <v>289046</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -6628,16 +6628,16 @@
         <v>62170</v>
       </c>
       <c r="E16" s="30">
-        <v>199295</v>
+        <v>200677</v>
       </c>
       <c r="F16" s="30">
-        <v>412717</v>
+        <v>417164</v>
       </c>
       <c r="G16" s="30">
-        <v>687808</v>
+        <v>697255</v>
       </c>
       <c r="H16" s="30">
-        <v>970045</v>
+        <v>986301</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -6703,19 +6703,19 @@
         <v>373</v>
       </c>
       <c r="D21" s="29">
-        <v>0.13663808664259927</v>
+        <v>0.13663808664259913</v>
       </c>
       <c r="E21" s="29">
-        <v>0.4043437853073026</v>
+        <v>0.4067620818062212</v>
       </c>
       <c r="F21" s="29">
-        <v>0.5023099573664649</v>
+        <v>0.5058728257176494</v>
       </c>
       <c r="G21" s="29">
-        <v>0.5551595361077036</v>
+        <v>0.5596038436877832</v>
       </c>
       <c r="H21" s="29">
-        <v>0.5541926962730911</v>
+        <v>0.5600748662293807</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -6809,7 +6809,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H39"/>
+  <dimension ref="B2:I39"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -6819,7 +6819,7 @@
     <col min="9" max="9" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="2" ht="30" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>376</v>
       </c>
@@ -6829,8 +6829,9 @@
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
-    </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B3" s="58" t="s">
         <v>377</v>
       </c>
@@ -6840,6 +6841,7 @@
       <c r="F3" s="58"/>
       <c r="G3" s="58"/>
       <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B4" s="59" t="s">
@@ -6900,19 +6902,19 @@
         <v>330</v>
       </c>
       <c r="C8" s="64">
-        <v>184666.6666666667</v>
+        <v>184666.66666666666</v>
       </c>
       <c r="D8" s="64">
-        <v>339129.56</v>
+        <v>340512</v>
       </c>
       <c r="E8" s="64">
-        <v>424882.21741599997</v>
+        <v>427945.8</v>
       </c>
       <c r="F8" s="64">
-        <v>495516.93485413</v>
+        <v>500517.5</v>
       </c>
       <c r="G8" s="64">
-        <v>509275.55642087164</v>
+        <v>516085</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
@@ -6926,10 +6928,10 @@
         <v>147002.63</v>
       </c>
       <c r="E9" s="64">
-        <v>151412.7089</v>
+        <v>151412.70889999997</v>
       </c>
       <c r="F9" s="64">
-        <v>155955.090167</v>
+        <v>155955.09016700002</v>
       </c>
       <c r="G9" s="64">
         <v>160633.74287201</v>
@@ -6980,19 +6982,19 @@
         <v>273</v>
       </c>
       <c r="C12" s="65">
-        <v>25232.5</v>
+        <v>25232.49999999997</v>
       </c>
       <c r="D12" s="65">
-        <v>137124.93</v>
+        <v>138507.37</v>
       </c>
       <c r="E12" s="65">
-        <v>213422.568516</v>
+        <v>216486.15110000002</v>
       </c>
       <c r="F12" s="65">
-        <v>275090.95168713003</v>
+        <v>280091.516833</v>
       </c>
       <c r="G12" s="65">
-        <v>282236.7937588616</v>
+        <v>289046.23733798997</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
@@ -7003,16 +7005,16 @@
         <v>62170</v>
       </c>
       <c r="D13" s="65">
-        <v>199294.93</v>
+        <v>200677.37</v>
       </c>
       <c r="E13" s="65">
-        <v>412717.498516</v>
+        <v>417163.5211</v>
       </c>
       <c r="F13" s="65">
-        <v>687808.45020313</v>
+        <v>697255.037933</v>
       </c>
       <c r="G13" s="65">
-        <v>970045.2439619916</v>
+        <v>986301.27527099</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
@@ -7020,19 +7022,19 @@
         <v>373</v>
       </c>
       <c r="C14" s="66">
-        <v>0.13663808664259927</v>
+        <v>0.13663808664259913</v>
       </c>
       <c r="D14" s="66">
-        <v>0.4043437853073026</v>
+        <v>0.4067620818062212</v>
       </c>
       <c r="E14" s="66">
-        <v>0.5023099573664649</v>
+        <v>0.5058728257176494</v>
       </c>
       <c r="F14" s="66">
-        <v>0.5551595361077036</v>
+        <v>0.5596038436877832</v>
       </c>
       <c r="G14" s="66">
-        <v>0.5541926962730911</v>
+        <v>0.5600748662293807</v>
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
@@ -7040,19 +7042,19 @@
         <v>239</v>
       </c>
       <c r="C15" s="67">
-        <v>15388.88888888889</v>
+        <v>15388.888888888889</v>
       </c>
       <c r="D15" s="67">
-        <v>18840.53111111111</v>
+        <v>18917.333333333332</v>
       </c>
       <c r="E15" s="67">
-        <v>19312.828064363635</v>
+        <v>19452.081818181818</v>
       </c>
       <c r="F15" s="67">
-        <v>19820.677394165203</v>
+        <v>20020.7</v>
       </c>
       <c r="G15" s="67">
-        <v>20371.022256834865</v>
+        <v>20643.4</v>
       </c>
       <c r="H15" s="68" t="s">
         <v>388</v>
@@ -7126,19 +7128,19 @@
         <v>392</v>
       </c>
       <c r="C19" s="71">
-        <v>2102.7083333333335</v>
+        <v>2102.7083333333308</v>
       </c>
       <c r="D19" s="71">
-        <v>7618.051666666666</v>
+        <v>7694.853888888889</v>
       </c>
       <c r="E19" s="71">
-        <v>9701.025841636363</v>
+        <v>9840.279595454545</v>
       </c>
       <c r="F19" s="71">
-        <v>11003.6380674852</v>
+        <v>11203.66067332</v>
       </c>
       <c r="G19" s="71">
-        <v>11289.471750354463</v>
+        <v>11561.8494935196</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
@@ -7146,19 +7148,19 @@
         <v>393</v>
       </c>
       <c r="C20" s="72">
-        <v>0.644047833935018</v>
+        <v>0.6440478339350181</v>
       </c>
       <c r="D20" s="66">
-        <v>0.43347041172111334</v>
+        <v>0.4317105711399305</v>
       </c>
       <c r="E20" s="66">
-        <v>0.35636395851265434</v>
+        <v>0.3538128167165094</v>
       </c>
       <c r="F20" s="66">
-        <v>0.314732109434181</v>
+        <v>0.31158768707787443</v>
       </c>
       <c r="G20" s="66">
-        <v>0.31541616487727187</v>
+        <v>0.3112544307081392</v>
       </c>
       <c r="H20" s="68" t="s">
         <v>394</v>
@@ -7169,19 +7171,19 @@
         <v>395</v>
       </c>
       <c r="C21" s="72">
-        <v>0.19494584837545123</v>
+        <v>0.19494584837545129</v>
       </c>
       <c r="D21" s="66">
-        <v>0.10933874357634882</v>
+        <v>0.10889484071045955</v>
       </c>
       <c r="E21" s="66">
-        <v>0.0898893821263553</v>
+        <v>0.0892458811372842</v>
       </c>
       <c r="F21" s="66">
-        <v>0.07938814848291784</v>
+        <v>0.07859499817688692</v>
       </c>
       <c r="G21" s="66">
-        <v>0.07956069489130392</v>
+        <v>0.07851093746185223</v>
       </c>
       <c r="H21" s="68" t="s">
         <v>396</v>
@@ -7192,19 +7194,19 @@
         <v>397</v>
       </c>
       <c r="C22" s="66">
-        <v>0.13663808664259935</v>
+        <v>0.13663808664259922</v>
       </c>
       <c r="D22" s="66">
-        <v>0.4043437853073026</v>
+        <v>0.4067620818062212</v>
       </c>
       <c r="E22" s="66">
-        <v>0.5023099573664649</v>
+        <v>0.5058728257176494</v>
       </c>
       <c r="F22" s="66">
-        <v>0.5551595361077037</v>
+        <v>0.5596038436877832</v>
       </c>
       <c r="G22" s="66">
-        <v>0.5541926962730912</v>
+        <v>0.5600748662293809</v>
       </c>
       <c r="H22" s="68" t="s">
         <v>398</v>
@@ -7294,14 +7296,14 @@
       <c r="D26" s="77">
         <v>12</v>
       </c>
-      <c r="E26" s="77">
-        <v>23</v>
+      <c r="E26" s="73">
+        <v>24</v>
       </c>
       <c r="F26" s="73">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G26" s="73">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H26" s="68" t="s">
         <v>403</v>
@@ -7315,22 +7317,22 @@
         <v>142</v>
       </c>
       <c r="D27" s="73">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="E27" s="73">
-        <v>712</v>
+        <v>720</v>
       </c>
       <c r="F27" s="73">
-        <v>1139</v>
+        <v>1155</v>
       </c>
       <c r="G27" s="73">
-        <v>1559</v>
+        <v>1586</v>
       </c>
       <c r="H27" s="68" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="29" ht="24" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B29" s="19" t="s">
         <v>405</v>
       </c>
@@ -7346,8 +7348,9 @@
       </c>
       <c r="G29" s="19"/>
       <c r="H29" s="19"/>
-    </row>
-    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I29" s="19"/>
+    </row>
+    <row r="30" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B30" s="44" t="s">
         <v>409</v>
       </c>
@@ -7363,8 +7366,9 @@
       </c>
       <c r="G30" s="79"/>
       <c r="H30" s="79"/>
-    </row>
-    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I30" s="79"/>
+    </row>
+    <row r="31" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B31" s="44" t="s">
         <v>413</v>
       </c>
@@ -7380,8 +7384,9 @@
       </c>
       <c r="G31" s="79"/>
       <c r="H31" s="79"/>
-    </row>
-    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I31" s="79"/>
+    </row>
+    <row r="32" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B32" s="44" t="s">
         <v>416</v>
       </c>
@@ -7397,8 +7402,9 @@
       </c>
       <c r="G32" s="79"/>
       <c r="H32" s="79"/>
-    </row>
-    <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I32" s="79"/>
+    </row>
+    <row r="33" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B33" s="44" t="s">
         <v>419</v>
       </c>
@@ -7414,8 +7420,9 @@
       </c>
       <c r="G33" s="79"/>
       <c r="H33" s="79"/>
-    </row>
-    <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I33" s="79"/>
+    </row>
+    <row r="34" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B34" s="44" t="s">
         <v>422</v>
       </c>
@@ -7431,8 +7438,9 @@
       </c>
       <c r="G34" s="79"/>
       <c r="H34" s="79"/>
-    </row>
-    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I34" s="79"/>
+    </row>
+    <row r="35" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B35" s="44" t="s">
         <v>425</v>
       </c>
@@ -7448,6 +7456,7 @@
       </c>
       <c r="G35" s="79"/>
       <c r="H35" s="79"/>
+      <c r="I35" s="79"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B37" s="44" t="s">
@@ -7460,7 +7469,7 @@
       <c r="E37" s="10"/>
       <c r="F37" s="10"/>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B39" s="80" t="s">
         <v>430</v>
       </c>
@@ -7470,27 +7479,28 @@
       <c r="F39" s="80"/>
       <c r="G39" s="80"/>
       <c r="H39" s="80"/>
+      <c r="I39" s="80"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B3:I3"/>
     <mergeCell ref="D29:E29"/>
-    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="F29:I29"/>
     <mergeCell ref="D30:E30"/>
-    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="F30:I30"/>
     <mergeCell ref="D31:E31"/>
-    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="F31:I31"/>
     <mergeCell ref="D32:E32"/>
-    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="F32:I32"/>
     <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="F33:I33"/>
     <mergeCell ref="D34:E34"/>
-    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="F34:I34"/>
     <mergeCell ref="D35:E35"/>
-    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="F35:I35"/>
     <mergeCell ref="C37:F37"/>
-    <mergeCell ref="B39:H39"/>
+    <mergeCell ref="B39:I39"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -8102,7 +8112,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
         <v>103</v>
       </c>
@@ -8111,7 +8121,6 @@
       <c r="D15" s="19"/>
       <c r="E15" s="19"/>
       <c r="F15" s="19"/>
-      <c r="G15" s="19"/>
     </row>
     <row r="16" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="21" t="s">
@@ -9015,7 +9024,7 @@
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
-    <col min="2" max="7" width="16" customWidth="1"/>
+    <col min="2" max="6" width="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9458,7 +9467,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="8" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="19" t="s">
         <v>216</v>
       </c>
@@ -9467,7 +9476,6 @@
       <c r="D8" s="19"/>
       <c r="E8" s="19"/>
       <c r="F8" s="19"/>
-      <c r="G8" s="19"/>
     </row>
     <row r="9" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="21" t="s">
@@ -9570,7 +9578,7 @@
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
-    <col min="2" max="7" width="16" customWidth="1"/>
+    <col min="2" max="6" width="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Microschool_With_Decisions.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Microschool_With_Decisions.xlsx
@@ -24,18 +24,19 @@
     <sheet sheetId="18" name="DSCR &amp; Covenants" state="visible" r:id="rId21"/>
     <sheet sheetId="19" name="Sources &amp; Uses" state="visible" r:id="rId22"/>
     <sheet sheetId="20" name="Scenarios" state="visible" r:id="rId23"/>
-    <sheet sheetId="21" name="Underwriting Snapshot" state="visible" r:id="rId24"/>
+    <sheet sheetId="21" name="Lender Snapshot" state="visible" r:id="rId24"/>
     <sheet sheetId="22" name="Financial Health" state="visible" r:id="rId25"/>
     <sheet sheetId="23" name="Budget Narrative" state="visible" r:id="rId26"/>
-    <sheet sheetId="24" name="Assumptions Memo" state="visible" r:id="rId27"/>
-    <sheet sheetId="25" name="Decision History" state="visible" r:id="rId28"/>
+    <sheet sheetId="24" name="Assumptions Confidence" state="visible" r:id="rId27"/>
+    <sheet sheetId="25" name="Assumptions Memo" state="visible" r:id="rId28"/>
+    <sheet sheetId="26" name="Decision History" state="visible" r:id="rId29"/>
   </sheets>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="838" uniqueCount="482">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="876" uniqueCount="505">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -43,7 +44,7 @@
     <t>Bright Horizons Microschool</t>
   </si>
   <si>
-    <t>Generated May 7, 2026 · llc_single</t>
+    <t>Generated May 9, 2026 · llc_single</t>
   </si>
   <si>
     <t>Cell Color Legend</t>
@@ -130,7 +131,7 @@
     <t>SchoolStack Budget</t>
   </si>
   <si>
-    <t>5-Year Financial Model &amp; Underwriting Workbook</t>
+    <t>5-Year Financial Model — Founder Planning Workbook</t>
   </si>
   <si>
     <t>School Name</t>
@@ -163,7 +164,7 @@
     <t>Model Date</t>
   </si>
   <si>
-    <t>May 7, 2026</t>
+    <t>May 9, 2026</t>
   </si>
   <si>
     <t>Stage</t>
@@ -304,7 +305,7 @@
     <t>21.</t>
   </si>
   <si>
-    <t>Underwriting Snapshot</t>
+    <t>Lender Snapshot</t>
   </si>
   <si>
     <t>22.</t>
@@ -319,6 +320,12 @@
     <t>Budget Narrative</t>
   </si>
   <si>
+    <t>24.</t>
+  </si>
+  <si>
+    <t>Assumptions Confidence</t>
+  </si>
+  <si>
     <t>CONFIDENTIAL - Prepared by SchoolStack Budget (budget.schoolstack.ai)</t>
   </si>
   <si>
@@ -427,6 +434,39 @@
     <t>% of Base</t>
   </si>
   <si>
+    <t>REVENUE QUALITY</t>
+  </si>
+  <si>
+    <t>Bucket</t>
+  </si>
+  <si>
+    <t>Contracted</t>
+  </si>
+  <si>
+    <t>Projected</t>
+  </si>
+  <si>
+    <t>Donor-dependent</t>
+  </si>
+  <si>
+    <t>Policy-dependent</t>
+  </si>
+  <si>
+    <t>Contracted %</t>
+  </si>
+  <si>
+    <t>Projected %</t>
+  </si>
+  <si>
+    <t>Donor-dependent %</t>
+  </si>
+  <si>
+    <t>Policy-dependent %</t>
+  </si>
+  <si>
+    <t>Hard Rev Coverage (Contracted ÷ Fixed + Debt)</t>
+  </si>
+  <si>
     <t>STAFFING</t>
   </si>
   <si>
@@ -940,7 +980,7 @@
     <t>Minimum Cash Month</t>
   </si>
   <si>
-    <t>Cash Trough: July (Month 1)</t>
+    <t>Cash Trough: September (Month 3)</t>
   </si>
   <si>
     <t>Your lowest cash point is the month lenders focus on to ensure you won't run out of money before collections start. Plan reserves to cover this trough.</t>
@@ -952,7 +992,10 @@
     <t>Projections prepared on an accrual basis. School currently keeps books on a undetermined basis.</t>
   </si>
   <si>
-    <t>Capital &amp; Debt Service</t>
+    <t>Interest Expense</t>
+  </si>
+  <si>
+    <t>Principal &amp; Capital Outlays</t>
   </si>
   <si>
     <t>Depreciation</t>
@@ -1051,6 +1094,9 @@
     <t>Ending Cash</t>
   </si>
   <si>
+    <t>Working-Capital Cash (basis for runway/days)</t>
+  </si>
+  <si>
     <t>Days Cash on Hand</t>
   </si>
   <si>
@@ -1135,7 +1181,7 @@
     <t>Enrollment: -20%  |  Revenue: +0%  |  Staffing: +0%  |  Facility: +0%  |  Expenses: +0%</t>
   </si>
   <si>
-    <t>Underwriting Snapshot - Loan Committee Summary</t>
+    <t>Lender Conversation Snapshot - Summary</t>
   </si>
   <si>
     <t>Entity</t>
@@ -1162,13 +1208,34 @@
     <t>Enrollment</t>
   </si>
   <si>
+    <t>BREAK-EVEN &amp; DOWNSIDE</t>
+  </si>
+  <si>
+    <t>Break-Even Students</t>
+  </si>
+  <si>
+    <t>Break-Even Utilization %</t>
+  </si>
+  <si>
+    <t>-10% Enrollment: DSCR</t>
+  </si>
+  <si>
+    <t>-10% Enrollment: Ending Cash</t>
+  </si>
+  <si>
+    <t>-20% Enrollment: DSCR</t>
+  </si>
+  <si>
+    <t>-20% Enrollment: Ending Cash</t>
+  </si>
+  <si>
     <t>Prepared by SchoolStack Budget - budget.schoolstack.ai</t>
   </si>
   <si>
     <t>Bright Horizons Microschool — Financial Health Dashboard</t>
   </si>
   <si>
-    <t>Generated May 7, 2026</t>
+    <t>Generated May 9, 2026</t>
   </si>
   <si>
     <t>● Green = healthy</t>
@@ -1358,6 +1425,9 @@
   </si>
   <si>
     <t>Additional Context</t>
+  </si>
+  <si>
+    <t>No assumptions tagged yet — open the wizard and tag each major assumption (Actuals, Signed agreement, Written quote, Research, Estimate) with a one-line evidence note. The tags surface here, in the lender PDF, and on share links.</t>
   </si>
   <si>
     <t>Assumptions Memo</t>
@@ -1496,14 +1566,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="#,##0;#,##0;&quot;-&quot;"/>
     <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* (#,##0);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="166" formatCode="0.0%;[Red](0.0%);&quot;-&quot;"/>
-    <numFmt numFmtId="167" formatCode="0.0"/>
-    <numFmt numFmtId="168" formatCode="0.00x"/>
+    <numFmt numFmtId="167" formatCode="0.00&quot;×&quot;"/>
+    <numFmt numFmtId="168" formatCode="0.0"/>
+    <numFmt numFmtId="169" formatCode="0.00x"/>
   </numFmts>
-  <fonts count="28" x14ac:knownFonts="1">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1597,11 +1668,6 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <color rgb="FFDC2626"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
       <i/>
       <color rgb="FF9CA3AF"/>
       <sz val="9"/>
@@ -1667,7 +1733,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1697,11 +1763,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1E293B"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEF2F2"/>
       </patternFill>
     </fill>
     <fill>
@@ -1800,24 +1861,24 @@
     <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="16" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1827,28 +1888,28 @@
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1867,17 +1928,17 @@
     <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1889,29 +1950,29 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1930,12 +1991,12 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -2634,7 +2695,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>236</v>
+        <v>249</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -2647,44 +2708,44 @@
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="B4" s="35">
+        <v>111</v>
+      </c>
+      <c r="B4" s="36">
         <v>12</v>
       </c>
-      <c r="C4" s="35">
+      <c r="C4" s="36">
         <v>18</v>
       </c>
-      <c r="D4" s="35">
+      <c r="D4" s="36">
         <v>22</v>
       </c>
-      <c r="E4" s="35">
+      <c r="E4" s="36">
         <v>25</v>
       </c>
-      <c r="F4" s="35">
+      <c r="F4" s="36">
         <v>25</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="19" t="s">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="B6" s="19"/>
       <c r="C6" s="19"/>
@@ -2694,146 +2755,146 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="B7" s="30">
+        <v>119</v>
+      </c>
+      <c r="B7" s="25">
         <v>144000</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="25">
         <v>222480</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="25">
         <v>280078</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="25">
         <v>327818</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="25">
         <v>337653</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="B8" s="30">
+        <v>123</v>
+      </c>
+      <c r="B8" s="25">
         <v>3000</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="25">
         <v>4635</v>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="25">
         <v>5835</v>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="25">
         <v>6830</v>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="25">
         <v>7034</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="B9" s="30">
+        <v>124</v>
+      </c>
+      <c r="B9" s="25">
         <v>84000</v>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="25">
         <v>129780</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="25">
         <v>163379</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="25">
         <v>191227</v>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="25">
         <v>196964</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="B10" s="30">
+        <v>126</v>
+      </c>
+      <c r="B10" s="25">
         <v>5000</v>
       </c>
-      <c r="C10" s="30">
+      <c r="C10" s="25">
         <v>5150</v>
       </c>
-      <c r="D10" s="30">
+      <c r="D10" s="25">
         <v>5305</v>
       </c>
-      <c r="E10" s="30">
+      <c r="E10" s="25">
         <v>5464</v>
       </c>
-      <c r="F10" s="30">
+      <c r="F10" s="25">
         <v>5628</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>127</v>
-      </c>
-      <c r="B11" s="30">
+        <v>129</v>
+      </c>
+      <c r="B11" s="25">
         <v>-10</v>
       </c>
-      <c r="C11" s="30">
+      <c r="C11" s="25">
         <v>-10</v>
       </c>
-      <c r="D11" s="30">
+      <c r="D11" s="25">
         <v>-11</v>
       </c>
-      <c r="E11" s="30">
+      <c r="E11" s="25">
         <v>-11</v>
       </c>
-      <c r="F11" s="30">
+      <c r="F11" s="25">
         <v>-11</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
-        <v>238</v>
-      </c>
-      <c r="B12" s="32">
+        <v>251</v>
+      </c>
+      <c r="B12" s="33">
         <f>SUM(B7:B11)</f>
         <v>221600</v>
       </c>
-      <c r="C12" s="32">
+      <c r="C12" s="33">
         <f>SUM(C7:C11)</f>
         <v>339130</v>
       </c>
-      <c r="D12" s="32">
+      <c r="D12" s="33">
         <f>SUM(D7:D11)</f>
         <v>424882</v>
       </c>
-      <c r="E12" s="32">
+      <c r="E12" s="33">
         <f>SUM(E7:E11)</f>
         <v>495517</v>
       </c>
-      <c r="F12" s="32">
+      <c r="F12" s="33">
         <f>SUM(F7:F11)</f>
         <v>509276</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>239</v>
-      </c>
-      <c r="B14" s="30">
+        <v>252</v>
+      </c>
+      <c r="B14" s="25">
         <v>18467</v>
       </c>
-      <c r="C14" s="30">
+      <c r="C14" s="25">
         <v>18841</v>
       </c>
-      <c r="D14" s="30">
+      <c r="D14" s="25">
         <v>19313</v>
       </c>
-      <c r="E14" s="30">
+      <c r="E14" s="25">
         <v>19821</v>
       </c>
-      <c r="F14" s="30">
+      <c r="F14" s="25">
         <v>20371</v>
       </c>
     </row>
@@ -2863,7 +2924,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -2876,24 +2937,24 @@
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -2903,72 +2964,72 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>241</v>
-      </c>
-      <c r="B5" s="30">
+        <v>254</v>
+      </c>
+      <c r="B5" s="25">
         <v>47869</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="25">
         <v>59166</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="25">
         <v>60941</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="25">
         <v>62769</v>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="25">
         <v>64652</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>242</v>
-      </c>
-      <c r="B6" s="30">
+        <v>255</v>
+      </c>
+      <c r="B6" s="25">
         <v>12559</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="25">
         <v>15523</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="25">
         <v>15989</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="25">
         <v>16468</v>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="25">
         <v>16963</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>243</v>
-      </c>
-      <c r="B7" s="31">
+        <v>256</v>
+      </c>
+      <c r="B7" s="32">
         <f>SUM(B5:B6)</f>
         <v>60428</v>
       </c>
-      <c r="C7" s="31">
+      <c r="C7" s="32">
         <f>SUM(C5:C6)</f>
         <v>74689</v>
       </c>
-      <c r="D7" s="31">
+      <c r="D7" s="32">
         <f>SUM(D5:D6)</f>
         <v>76930</v>
       </c>
-      <c r="E7" s="31">
+      <c r="E7" s="32">
         <f>SUM(E5:E6)</f>
         <v>79237</v>
       </c>
-      <c r="F7" s="31">
+      <c r="F7" s="32">
         <f>SUM(F5:F6)</f>
         <v>81615</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="19" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="B8" s="19"/>
       <c r="C8" s="19"/>
@@ -2978,70 +3039,70 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>244</v>
-      </c>
-      <c r="B9" s="30">
+        <v>257</v>
+      </c>
+      <c r="B9" s="25">
         <v>58506</v>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="25">
         <v>72314</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="25">
         <v>74483</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="25">
         <v>76718</v>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="25">
         <v>79019</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>245</v>
-      </c>
-      <c r="B10" s="31">
+        <v>258</v>
+      </c>
+      <c r="B10" s="32">
         <f>SUM(B9:B9)</f>
         <v>58506</v>
       </c>
-      <c r="C10" s="31">
+      <c r="C10" s="32">
         <f>SUM(C9:C9)</f>
         <v>72314</v>
       </c>
-      <c r="D10" s="31">
+      <c r="D10" s="32">
         <f>SUM(D9:D9)</f>
         <v>74483</v>
       </c>
-      <c r="E10" s="31">
+      <c r="E10" s="32">
         <f>SUM(E9:E9)</f>
         <v>76718</v>
       </c>
-      <c r="F10" s="31">
+      <c r="F10" s="32">
         <f>SUM(F9:F9)</f>
         <v>79019</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
-        <v>246</v>
-      </c>
-      <c r="B12" s="32">
+        <v>259</v>
+      </c>
+      <c r="B12" s="33">
         <f>B7+B10</f>
         <v>118934</v>
       </c>
-      <c r="C12" s="32">
+      <c r="C12" s="33">
         <f>C7+C10</f>
         <v>147003</v>
       </c>
-      <c r="D12" s="32">
+      <c r="D12" s="33">
         <f>D7+D10</f>
         <v>151413</v>
       </c>
-      <c r="E12" s="32">
+      <c r="E12" s="33">
         <f>E7+E10</f>
         <v>155955</v>
       </c>
-      <c r="F12" s="32">
+      <c r="F12" s="33">
         <f>F7+F10</f>
         <v>160634</v>
       </c>
@@ -3072,7 +3133,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -3085,24 +3146,24 @@
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>248</v>
+        <v>261</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -3112,132 +3173,132 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>249</v>
-      </c>
-      <c r="B5" s="30">
+        <v>262</v>
+      </c>
+      <c r="B5" s="25">
         <v>120000</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="25">
         <v>222480</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="25">
         <v>280078</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="25">
         <v>327818</v>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="25">
         <v>337653</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>250</v>
-      </c>
-      <c r="B6" s="30">
+        <v>263</v>
+      </c>
+      <c r="B6" s="25">
         <v>2500</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="25">
         <v>4635</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="25">
         <v>5835</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="25">
         <v>6830</v>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="25">
         <v>7034</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>251</v>
-      </c>
-      <c r="B7" s="30">
+        <v>264</v>
+      </c>
+      <c r="B7" s="25">
         <v>70000</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="25">
         <v>129780</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="25">
         <v>163379</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="25">
         <v>191227</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="25">
         <v>196964</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>252</v>
-      </c>
-      <c r="B8" s="30">
+        <v>265</v>
+      </c>
+      <c r="B8" s="25">
         <v>4167</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="25">
         <v>5150</v>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="25">
         <v>5305</v>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="25">
         <v>5464</v>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="25">
         <v>5628</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>253</v>
-      </c>
-      <c r="B9" s="30">
+        <v>266</v>
+      </c>
+      <c r="B9" s="25">
         <v>-8</v>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="25">
         <v>-10</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="25">
         <v>-11</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="25">
         <v>-11</v>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="25">
         <v>-11</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>254</v>
-      </c>
-      <c r="B10" s="31">
+        <v>267</v>
+      </c>
+      <c r="B10" s="32">
         <f>SUM(B5:B9)</f>
         <v>184667</v>
       </c>
-      <c r="C10" s="31">
+      <c r="C10" s="32">
         <f>SUM(C5:C9)</f>
         <v>340512</v>
       </c>
-      <c r="D10" s="31">
+      <c r="D10" s="32">
         <f>SUM(D5:D9)</f>
         <v>427946</v>
       </c>
-      <c r="E10" s="31">
+      <c r="E10" s="32">
         <f>SUM(E5:E9)</f>
         <v>500518</v>
       </c>
-      <c r="F10" s="31">
+      <c r="F10" s="32">
         <f>SUM(F5:F9)</f>
         <v>516085</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
-        <v>255</v>
+        <v>268</v>
       </c>
       <c r="B12" s="19"/>
       <c r="C12" s="19"/>
@@ -3247,92 +3308,92 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>256</v>
-      </c>
-      <c r="B13" s="30">
+        <v>269</v>
+      </c>
+      <c r="B13" s="25">
         <v>58506</v>
       </c>
-      <c r="C13" s="30">
+      <c r="C13" s="25">
         <v>72314</v>
       </c>
-      <c r="D13" s="30">
+      <c r="D13" s="25">
         <v>74483</v>
       </c>
-      <c r="E13" s="30">
+      <c r="E13" s="25">
         <v>76718</v>
       </c>
-      <c r="F13" s="30">
+      <c r="F13" s="25">
         <v>79019</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>257</v>
-      </c>
-      <c r="B14" s="30">
+        <v>270</v>
+      </c>
+      <c r="B14" s="25">
         <v>47869</v>
       </c>
-      <c r="C14" s="30">
+      <c r="C14" s="25">
         <v>59166</v>
       </c>
-      <c r="D14" s="30">
+      <c r="D14" s="25">
         <v>60941</v>
       </c>
-      <c r="E14" s="30">
+      <c r="E14" s="25">
         <v>62769</v>
       </c>
-      <c r="F14" s="30">
+      <c r="F14" s="25">
         <v>64652</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>258</v>
-      </c>
-      <c r="B15" s="30">
+        <v>271</v>
+      </c>
+      <c r="B15" s="25">
         <v>12559</v>
       </c>
-      <c r="C15" s="30">
+      <c r="C15" s="25">
         <v>15523</v>
       </c>
-      <c r="D15" s="30">
+      <c r="D15" s="25">
         <v>15989</v>
       </c>
-      <c r="E15" s="30">
+      <c r="E15" s="25">
         <v>16468</v>
       </c>
-      <c r="F15" s="30">
+      <c r="F15" s="25">
         <v>16963</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="B16" s="31">
+        <v>230</v>
+      </c>
+      <c r="B16" s="32">
         <f>SUM(B13:B15)</f>
         <v>118934</v>
       </c>
-      <c r="C16" s="31">
+      <c r="C16" s="32">
         <f>SUM(C13:C15)</f>
         <v>147003</v>
       </c>
-      <c r="D16" s="31">
+      <c r="D16" s="32">
         <f>SUM(D13:D15)</f>
         <v>151413</v>
       </c>
-      <c r="E16" s="31">
+      <c r="E16" s="32">
         <f>SUM(E13:E15)</f>
         <v>155955</v>
       </c>
-      <c r="F16" s="31">
+      <c r="F16" s="32">
         <f>SUM(F13:F15)</f>
         <v>160634</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="19" t="s">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="B18" s="19"/>
       <c r="C18" s="19"/>
@@ -3341,198 +3402,198 @@
       <c r="F18" s="19"/>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="36" t="s">
-        <v>151</v>
+      <c r="A19" s="37" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>259</v>
-      </c>
-      <c r="B20" s="30">
+        <v>272</v>
+      </c>
+      <c r="B20" s="25">
         <v>5000</v>
       </c>
-      <c r="C20" s="30">
+      <c r="C20" s="25">
         <v>9270</v>
       </c>
-      <c r="D20" s="30">
+      <c r="D20" s="25">
         <v>11670</v>
       </c>
-      <c r="E20" s="30">
+      <c r="E20" s="25">
         <v>13659</v>
       </c>
-      <c r="F20" s="30">
+      <c r="F20" s="25">
         <v>14069</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="36" t="s">
-        <v>152</v>
+      <c r="A21" s="37" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>260</v>
-      </c>
-      <c r="B22" s="30">
+        <v>273</v>
+      </c>
+      <c r="B22" s="25">
         <v>3000</v>
       </c>
-      <c r="C22" s="30">
+      <c r="C22" s="25">
         <v>5562</v>
       </c>
-      <c r="D22" s="30">
+      <c r="D22" s="25">
         <v>7002</v>
       </c>
-      <c r="E22" s="30">
+      <c r="E22" s="25">
         <v>8195</v>
       </c>
-      <c r="F22" s="30">
+      <c r="F22" s="25">
         <v>8441</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="36" t="s">
-        <v>146</v>
+      <c r="A23" s="37" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
-        <v>261</v>
-      </c>
-      <c r="B24" s="30">
+        <v>274</v>
+      </c>
+      <c r="B24" s="25">
         <v>25000</v>
       </c>
-      <c r="C24" s="30">
+      <c r="C24" s="25">
         <v>30900</v>
       </c>
-      <c r="D24" s="30">
+      <c r="D24" s="25">
         <v>31827</v>
       </c>
-      <c r="E24" s="30">
+      <c r="E24" s="25">
         <v>32782</v>
       </c>
-      <c r="F24" s="30">
+      <c r="F24" s="25">
         <v>33765</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
-        <v>262</v>
-      </c>
-      <c r="B25" s="30">
+        <v>275</v>
+      </c>
+      <c r="B25" s="25">
         <v>3000</v>
       </c>
-      <c r="C25" s="30">
+      <c r="C25" s="25">
         <v>3708</v>
       </c>
-      <c r="D25" s="30">
+      <c r="D25" s="25">
         <v>3819</v>
       </c>
-      <c r="E25" s="30">
+      <c r="E25" s="25">
         <v>3934</v>
       </c>
-      <c r="F25" s="30">
+      <c r="F25" s="25">
         <v>4052</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
-        <v>263</v>
-      </c>
-      <c r="B26" s="30">
+        <v>276</v>
+      </c>
+      <c r="B26" s="25">
         <v>2000</v>
       </c>
-      <c r="C26" s="30">
+      <c r="C26" s="25">
         <v>2472</v>
       </c>
-      <c r="D26" s="30">
+      <c r="D26" s="25">
         <v>2546</v>
       </c>
-      <c r="E26" s="30">
+      <c r="E26" s="25">
         <v>2623</v>
       </c>
-      <c r="F26" s="30">
+      <c r="F26" s="25">
         <v>2701</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
-        <v>264</v>
-      </c>
-      <c r="B27" s="31">
+        <v>277</v>
+      </c>
+      <c r="B27" s="32">
         <f>SUM(B24:B26)</f>
         <v>30000</v>
       </c>
-      <c r="C27" s="31">
+      <c r="C27" s="32">
         <f>SUM(C24:C26)</f>
         <v>37080</v>
       </c>
-      <c r="D27" s="31">
+      <c r="D27" s="32">
         <f>SUM(D24:D26)</f>
         <v>38192</v>
       </c>
-      <c r="E27" s="31">
+      <c r="E27" s="32">
         <f>SUM(E24:E26)</f>
         <v>39338</v>
       </c>
-      <c r="F27" s="31">
+      <c r="F27" s="32">
         <f>SUM(F24:F26)</f>
         <v>40518</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" s="36" t="s">
-        <v>154</v>
+      <c r="A28" s="37" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
-        <v>265</v>
-      </c>
-      <c r="B29" s="30">
+        <v>278</v>
+      </c>
+      <c r="B29" s="25">
         <v>2500</v>
       </c>
-      <c r="C29" s="30">
+      <c r="C29" s="25">
         <v>3090</v>
       </c>
-      <c r="D29" s="30">
+      <c r="D29" s="25">
         <v>3183</v>
       </c>
-      <c r="E29" s="30">
+      <c r="E29" s="25">
         <v>3278</v>
       </c>
-      <c r="F29" s="30">
+      <c r="F29" s="25">
         <v>3377</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
-        <v>266</v>
-      </c>
-      <c r="B30" s="31">
+        <v>279</v>
+      </c>
+      <c r="B30" s="32">
         <f>B20+B22+B27+B29</f>
         <v>40500</v>
       </c>
-      <c r="C30" s="31">
+      <c r="C30" s="32">
         <f>C20+C22+C27+C29</f>
         <v>55002</v>
       </c>
-      <c r="D30" s="31">
+      <c r="D30" s="32">
         <f>D20+D22+D27+D29</f>
         <v>60047</v>
       </c>
-      <c r="E30" s="31">
+      <c r="E30" s="32">
         <f>E20+E22+E27+E29</f>
         <v>64471</v>
       </c>
-      <c r="F30" s="31">
+      <c r="F30" s="32">
         <f>F20+F22+F27+F29</f>
         <v>66405</v>
       </c>
     </row>
     <row r="32" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="19" t="s">
-        <v>267</v>
+        <v>280</v>
       </c>
       <c r="B32" s="19"/>
       <c r="C32" s="19"/>
@@ -3542,25 +3603,25 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
-        <v>268</v>
-      </c>
-      <c r="B33" s="31" t="str">
+        <v>281</v>
+      </c>
+      <c r="B33" s="32" t="str">
         <f>SUM(B33:B32)</f>
         <v>0</v>
       </c>
-      <c r="C33" s="31" t="str">
+      <c r="C33" s="32" t="str">
         <f>SUM(C33:C32)</f>
         <v>0</v>
       </c>
-      <c r="D33" s="31" t="str">
+      <c r="D33" s="32" t="str">
         <f>SUM(D33:D32)</f>
         <v>0</v>
       </c>
-      <c r="E33" s="31" t="str">
+      <c r="E33" s="32" t="str">
         <f>SUM(E33:E32)</f>
         <v>0</v>
       </c>
-      <c r="F33" s="31" t="str">
+      <c r="F33" s="32" t="str">
         <f>SUM(F33:F32)</f>
         <v>0</v>
       </c>
@@ -3591,7 +3652,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>269</v>
+        <v>282</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -3604,149 +3665,149 @@
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>254</v>
-      </c>
-      <c r="B4" s="33">
+        <v>267</v>
+      </c>
+      <c r="B4" s="34">
         <f>'Budget Detail'!B10</f>
         <v>184667</v>
       </c>
-      <c r="C4" s="33">
+      <c r="C4" s="34">
         <f>'Budget Detail'!C10</f>
         <v>340512</v>
       </c>
-      <c r="D4" s="33">
+      <c r="D4" s="34">
         <f>'Budget Detail'!D10</f>
         <v>427946</v>
       </c>
-      <c r="E4" s="33">
+      <c r="E4" s="34">
         <f>'Budget Detail'!E10</f>
         <v>500518</v>
       </c>
-      <c r="F4" s="33">
+      <c r="F4" s="34">
         <f>'Budget Detail'!F10</f>
         <v>516085</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="B5" s="33">
+        <v>230</v>
+      </c>
+      <c r="B5" s="34">
         <f>'Budget Detail'!B16</f>
         <v>118934</v>
       </c>
-      <c r="C5" s="33">
+      <c r="C5" s="34">
         <f>'Budget Detail'!C16</f>
         <v>147003</v>
       </c>
-      <c r="D5" s="33">
+      <c r="D5" s="34">
         <f>'Budget Detail'!D16</f>
         <v>151413</v>
       </c>
-      <c r="E5" s="33">
+      <c r="E5" s="34">
         <f>'Budget Detail'!E16</f>
         <v>155955</v>
       </c>
-      <c r="F5" s="33">
+      <c r="F5" s="34">
         <f>'Budget Detail'!F16</f>
         <v>160634</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>266</v>
-      </c>
-      <c r="B6" s="33">
+        <v>279</v>
+      </c>
+      <c r="B6" s="34">
         <f>'Budget Detail'!B30</f>
         <v>40500</v>
       </c>
-      <c r="C6" s="33">
+      <c r="C6" s="34">
         <f>'Budget Detail'!C30</f>
         <v>55002</v>
       </c>
-      <c r="D6" s="33">
+      <c r="D6" s="34">
         <f>'Budget Detail'!D30</f>
         <v>60047</v>
       </c>
-      <c r="E6" s="33">
+      <c r="E6" s="34">
         <f>'Budget Detail'!E30</f>
         <v>64471</v>
       </c>
-      <c r="F6" s="33">
+      <c r="F6" s="34">
         <f>'Budget Detail'!F30</f>
         <v>66405</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>270</v>
-      </c>
-      <c r="B7" s="33" t="str">
+        <v>283</v>
+      </c>
+      <c r="B7" s="34" t="str">
         <f>'Budget Detail'!B33</f>
         <v>0</v>
       </c>
-      <c r="C7" s="33" t="str">
+      <c r="C7" s="34" t="str">
         <f>'Budget Detail'!C33</f>
         <v>0</v>
       </c>
-      <c r="D7" s="33" t="str">
+      <c r="D7" s="34" t="str">
         <f>'Budget Detail'!D33</f>
         <v>0</v>
       </c>
-      <c r="E7" s="33" t="str">
+      <c r="E7" s="34" t="str">
         <f>'Budget Detail'!E33</f>
         <v>0</v>
       </c>
-      <c r="F7" s="33" t="str">
+      <c r="F7" s="34" t="str">
         <f>'Budget Detail'!F33</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>271</v>
-      </c>
-      <c r="B8" s="31">
+        <v>284</v>
+      </c>
+      <c r="B8" s="32">
         <f>SUM(B5:B7)</f>
         <v>159434</v>
       </c>
-      <c r="C8" s="31">
+      <c r="C8" s="32">
         <f>SUM(C5:C7)</f>
         <v>202005</v>
       </c>
-      <c r="D8" s="31">
+      <c r="D8" s="32">
         <f>SUM(D5:D7)</f>
         <v>211460</v>
       </c>
-      <c r="E8" s="31">
+      <c r="E8" s="32">
         <f>SUM(E5:E7)</f>
         <v>220426</v>
       </c>
-      <c r="F8" s="31">
+      <c r="F8" s="32">
         <f>SUM(F5:F7)</f>
         <v>227039</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
-        <v>272</v>
+        <v>285</v>
       </c>
       <c r="B10" s="19"/>
       <c r="C10" s="19"/>
@@ -3756,111 +3817,111 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>273</v>
-      </c>
-      <c r="B11" s="32">
+        <v>286</v>
+      </c>
+      <c r="B11" s="33">
         <f>B4-B8</f>
         <v>25232</v>
       </c>
-      <c r="C11" s="32">
+      <c r="C11" s="33">
         <f>C4-C8</f>
         <v>138507</v>
       </c>
-      <c r="D11" s="32">
+      <c r="D11" s="33">
         <f>D4-D8</f>
         <v>216486</v>
       </c>
-      <c r="E11" s="32">
+      <c r="E11" s="33">
         <f>E4-E8</f>
         <v>280092</v>
       </c>
-      <c r="F11" s="32">
+      <c r="F11" s="33">
         <f>F4-F8</f>
         <v>289046</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>274</v>
-      </c>
-      <c r="B12" s="29">
+        <v>287</v>
+      </c>
+      <c r="B12" s="26">
         <f>IF(B4=0,0,B11/B4)</f>
         <v>0.13663809</v>
       </c>
-      <c r="C12" s="29">
+      <c r="C12" s="26">
         <f>IF(C4=0,0,C11/C4)</f>
         <v>0.40676208</v>
       </c>
-      <c r="D12" s="29">
+      <c r="D12" s="26">
         <f>IF(D4=0,0,D11/D4)</f>
         <v>0.50587283</v>
       </c>
-      <c r="E12" s="29">
+      <c r="E12" s="26">
         <f>IF(E4=0,0,E11/E4)</f>
         <v>0.55960384</v>
       </c>
-      <c r="F12" s="29">
+      <c r="F12" s="26">
         <f>IF(F4=0,0,F11/F4)</f>
         <v>0.56007487</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>275</v>
-      </c>
-      <c r="B13" s="30">
+        <v>288</v>
+      </c>
+      <c r="B13" s="25">
         <v>25232</v>
       </c>
-      <c r="C13" s="30">
+      <c r="C13" s="25">
         <v>163740</v>
       </c>
-      <c r="D13" s="30">
+      <c r="D13" s="25">
         <v>380226</v>
       </c>
-      <c r="E13" s="30">
+      <c r="E13" s="25">
         <v>660318</v>
       </c>
-      <c r="F13" s="30">
+      <c r="F13" s="25">
         <v>949364</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>239</v>
-      </c>
-      <c r="B14" s="30">
+        <v>252</v>
+      </c>
+      <c r="B14" s="25">
         <v>15389</v>
       </c>
-      <c r="C14" s="30">
+      <c r="C14" s="25">
         <v>18917</v>
       </c>
-      <c r="D14" s="30">
+      <c r="D14" s="25">
         <v>19452</v>
       </c>
-      <c r="E14" s="30">
+      <c r="E14" s="25">
         <v>20021</v>
       </c>
-      <c r="F14" s="30">
+      <c r="F14" s="25">
         <v>20643</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>276</v>
-      </c>
-      <c r="B15" s="30">
+        <v>289</v>
+      </c>
+      <c r="B15" s="25">
         <v>13286</v>
       </c>
-      <c r="C15" s="30">
+      <c r="C15" s="25">
         <v>11222</v>
       </c>
-      <c r="D15" s="30">
+      <c r="D15" s="25">
         <v>9612</v>
       </c>
-      <c r="E15" s="30">
+      <c r="E15" s="25">
         <v>8817</v>
       </c>
-      <c r="F15" s="30">
+      <c r="F15" s="25">
         <v>9082</v>
       </c>
     </row>
@@ -3891,7 +3952,7 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>277</v>
+        <v>290</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -3912,48 +3973,48 @@
         <v>7</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>278</v>
+        <v>291</v>
       </c>
       <c r="C2" s="21" t="s">
-        <v>279</v>
+        <v>292</v>
       </c>
       <c r="D2" s="21" t="s">
-        <v>280</v>
+        <v>293</v>
       </c>
       <c r="E2" s="21" t="s">
-        <v>281</v>
+        <v>294</v>
       </c>
       <c r="F2" s="21" t="s">
-        <v>282</v>
+        <v>295</v>
       </c>
       <c r="G2" s="21" t="s">
-        <v>283</v>
+        <v>296</v>
       </c>
       <c r="H2" s="21" t="s">
-        <v>284</v>
+        <v>297</v>
       </c>
       <c r="I2" s="21" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="J2" s="21" t="s">
-        <v>286</v>
+        <v>299</v>
       </c>
       <c r="K2" s="21" t="s">
-        <v>287</v>
+        <v>300</v>
       </c>
       <c r="L2" s="21" t="s">
-        <v>288</v>
+        <v>301</v>
       </c>
       <c r="M2" s="21" t="s">
-        <v>289</v>
+        <v>302</v>
       </c>
       <c r="N2" s="21" t="s">
-        <v>290</v>
+        <v>303</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>248</v>
+        <v>261</v>
       </c>
       <c r="B3" s="19"/>
       <c r="C3" s="19"/>
@@ -3971,52 +4032,52 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>254</v>
-      </c>
-      <c r="B4" s="31">
-        <v>9150</v>
-      </c>
-      <c r="C4" s="31">
-        <v>22110</v>
-      </c>
-      <c r="D4" s="31">
-        <v>22110</v>
-      </c>
-      <c r="E4" s="31">
-        <v>22110</v>
-      </c>
-      <c r="F4" s="31">
-        <v>22110</v>
-      </c>
-      <c r="G4" s="31">
-        <v>22110</v>
-      </c>
-      <c r="H4" s="31">
-        <v>22110</v>
-      </c>
-      <c r="I4" s="31">
-        <v>22110</v>
-      </c>
-      <c r="J4" s="31">
-        <v>22110</v>
-      </c>
-      <c r="K4" s="31">
-        <v>22110</v>
-      </c>
-      <c r="L4" s="31">
+        <v>267</v>
+      </c>
+      <c r="B4" s="32">
+        <v>26250</v>
+      </c>
+      <c r="C4" s="32">
         <v>13210</v>
       </c>
-      <c r="M4" s="31">
+      <c r="D4" s="32">
+        <v>13210</v>
+      </c>
+      <c r="E4" s="32">
+        <v>34210</v>
+      </c>
+      <c r="F4" s="32">
+        <v>13210</v>
+      </c>
+      <c r="G4" s="32">
+        <v>13210</v>
+      </c>
+      <c r="H4" s="32">
+        <v>34210</v>
+      </c>
+      <c r="I4" s="32">
+        <v>13210</v>
+      </c>
+      <c r="J4" s="32">
+        <v>13210</v>
+      </c>
+      <c r="K4" s="32">
+        <v>34210</v>
+      </c>
+      <c r="L4" s="32">
+        <v>13210</v>
+      </c>
+      <c r="M4" s="32">
         <v>250</v>
       </c>
-      <c r="N4" s="31">
+      <c r="N4" s="32">
         <f>SUM(B4:M4)</f>
         <v>221600</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="19" t="s">
-        <v>291</v>
+        <v>304</v>
       </c>
       <c r="B6" s="19"/>
       <c r="C6" s="19"/>
@@ -4034,142 +4095,142 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>292</v>
-      </c>
-      <c r="B7" s="30">
+        <v>305</v>
+      </c>
+      <c r="B7" s="25">
         <v>11893</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="25">
         <v>11893</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="25">
         <v>11893</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="25">
         <v>11893</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="25">
         <v>11893</v>
       </c>
-      <c r="G7" s="30">
+      <c r="G7" s="25">
         <v>11893</v>
       </c>
-      <c r="H7" s="30">
+      <c r="H7" s="25">
         <v>11893</v>
       </c>
-      <c r="I7" s="30">
+      <c r="I7" s="25">
         <v>11893</v>
       </c>
-      <c r="J7" s="30">
+      <c r="J7" s="25">
         <v>11893</v>
       </c>
-      <c r="K7" s="30">
+      <c r="K7" s="25">
         <v>11893</v>
       </c>
-      <c r="L7" s="30">
+      <c r="L7" s="25">
         <v>0</v>
       </c>
-      <c r="M7" s="30">
+      <c r="M7" s="25">
         <v>0</v>
       </c>
-      <c r="N7" s="30">
+      <c r="N7" s="25">
         <f>SUM(B7:M7)</f>
         <v>118934</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>293</v>
-      </c>
-      <c r="B8" s="30">
+        <v>306</v>
+      </c>
+      <c r="B8" s="25">
         <v>4050</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="25">
         <v>4050</v>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="25">
         <v>4050</v>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="25">
         <v>4050</v>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="25">
         <v>4050</v>
       </c>
-      <c r="G8" s="30">
+      <c r="G8" s="25">
         <v>4050</v>
       </c>
-      <c r="H8" s="30">
+      <c r="H8" s="25">
         <v>4050</v>
       </c>
-      <c r="I8" s="30">
+      <c r="I8" s="25">
         <v>4050</v>
       </c>
-      <c r="J8" s="30">
+      <c r="J8" s="25">
         <v>4050</v>
       </c>
-      <c r="K8" s="30">
+      <c r="K8" s="25">
         <v>4050</v>
       </c>
-      <c r="L8" s="30">
+      <c r="L8" s="25">
         <v>0</v>
       </c>
-      <c r="M8" s="30">
+      <c r="M8" s="25">
         <v>0</v>
       </c>
-      <c r="N8" s="30">
+      <c r="N8" s="25">
         <f>SUM(B8:M8)</f>
         <v>40500</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>294</v>
-      </c>
-      <c r="B9" s="30">
+        <v>307</v>
+      </c>
+      <c r="B9" s="25">
         <v>0</v>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="25">
         <v>0</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="25">
         <v>0</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="25">
         <v>0</v>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="25">
         <v>0</v>
       </c>
-      <c r="G9" s="30">
+      <c r="G9" s="25">
         <v>0</v>
       </c>
-      <c r="H9" s="30">
+      <c r="H9" s="25">
         <v>0</v>
       </c>
-      <c r="I9" s="30">
+      <c r="I9" s="25">
         <v>0</v>
       </c>
-      <c r="J9" s="30">
+      <c r="J9" s="25">
         <v>0</v>
       </c>
-      <c r="K9" s="30">
+      <c r="K9" s="25">
         <v>0</v>
       </c>
-      <c r="L9" s="30">
+      <c r="L9" s="25">
         <v>0</v>
       </c>
-      <c r="M9" s="30">
+      <c r="M9" s="25">
         <v>0</v>
       </c>
-      <c r="N9" s="30" t="str">
+      <c r="N9" s="25" t="str">
         <f>SUM(B9:M9)</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>295</v>
+        <v>308</v>
       </c>
       <c r="B11" s="19"/>
       <c r="C11" s="19"/>
@@ -4187,185 +4248,185 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>271</v>
-      </c>
-      <c r="B12" s="33">
+        <v>284</v>
+      </c>
+      <c r="B12" s="34">
         <f>B7+B8+B9</f>
         <v>15943</v>
       </c>
-      <c r="C12" s="33">
+      <c r="C12" s="34">
         <f>C7+C8+C9</f>
         <v>15943</v>
       </c>
-      <c r="D12" s="33">
+      <c r="D12" s="34">
         <f>D7+D8+D9</f>
         <v>15943</v>
       </c>
-      <c r="E12" s="33">
+      <c r="E12" s="34">
         <f>E7+E8+E9</f>
         <v>15943</v>
       </c>
-      <c r="F12" s="33">
+      <c r="F12" s="34">
         <f>F7+F8+F9</f>
         <v>15943</v>
       </c>
-      <c r="G12" s="33">
+      <c r="G12" s="34">
         <f>G7+G8+G9</f>
         <v>15943</v>
       </c>
-      <c r="H12" s="33">
+      <c r="H12" s="34">
         <f>H7+H8+H9</f>
         <v>15943</v>
       </c>
-      <c r="I12" s="33">
+      <c r="I12" s="34">
         <f>I7+I8+I9</f>
         <v>15943</v>
       </c>
-      <c r="J12" s="33">
+      <c r="J12" s="34">
         <f>J7+J8+J9</f>
         <v>15943</v>
       </c>
-      <c r="K12" s="33">
+      <c r="K12" s="34">
         <f>K7+K8+K9</f>
         <v>15943</v>
       </c>
-      <c r="L12" s="33" t="str">
+      <c r="L12" s="34" t="str">
         <f>L7+L8+L9</f>
         <v>0</v>
       </c>
-      <c r="M12" s="33" t="str">
+      <c r="M12" s="34" t="str">
         <f>M7+M8+M9</f>
         <v>0</v>
       </c>
-      <c r="N12" s="33">
+      <c r="N12" s="34">
         <f>SUM(B12:M12)</f>
         <v>159430</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>296</v>
-      </c>
-      <c r="B13" s="33">
+        <v>309</v>
+      </c>
+      <c r="B13" s="34">
         <f>B4-B12</f>
-        <v>-6793</v>
-      </c>
-      <c r="C13" s="33">
+        <v>10307</v>
+      </c>
+      <c r="C13" s="34">
         <f>C4-C12</f>
-        <v>6167</v>
-      </c>
-      <c r="D13" s="33">
+        <v>-2733</v>
+      </c>
+      <c r="D13" s="34">
         <f>D4-D12</f>
-        <v>6167</v>
-      </c>
-      <c r="E13" s="33">
+        <v>-2733</v>
+      </c>
+      <c r="E13" s="34">
         <f>E4-E12</f>
-        <v>6167</v>
-      </c>
-      <c r="F13" s="33">
+        <v>18267</v>
+      </c>
+      <c r="F13" s="34">
         <f>F4-F12</f>
-        <v>6167</v>
-      </c>
-      <c r="G13" s="33">
+        <v>-2733</v>
+      </c>
+      <c r="G13" s="34">
         <f>G4-G12</f>
-        <v>6167</v>
-      </c>
-      <c r="H13" s="33">
+        <v>-2733</v>
+      </c>
+      <c r="H13" s="34">
         <f>H4-H12</f>
-        <v>6167</v>
-      </c>
-      <c r="I13" s="33">
+        <v>18267</v>
+      </c>
+      <c r="I13" s="34">
         <f>I4-I12</f>
-        <v>6167</v>
-      </c>
-      <c r="J13" s="33">
+        <v>-2733</v>
+      </c>
+      <c r="J13" s="34">
         <f>J4-J12</f>
-        <v>6167</v>
-      </c>
-      <c r="K13" s="33">
+        <v>-2733</v>
+      </c>
+      <c r="K13" s="34">
         <f>K4-K12</f>
-        <v>6167</v>
-      </c>
-      <c r="L13" s="33">
+        <v>18267</v>
+      </c>
+      <c r="L13" s="34">
         <f>L4-L12</f>
         <v>13210</v>
       </c>
-      <c r="M13" s="33">
+      <c r="M13" s="34">
         <f>M4-M12</f>
         <v>250</v>
       </c>
-      <c r="N13" s="33">
+      <c r="N13" s="34">
         <f>SUM(B13:M13)</f>
         <v>62170</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>297</v>
-      </c>
-      <c r="B14" s="37">
+        <v>310</v>
+      </c>
+      <c r="B14" s="38">
         <f>B17+B13</f>
-        <v>-6793</v>
-      </c>
-      <c r="C14" s="37">
+        <v>10307</v>
+      </c>
+      <c r="C14" s="38">
         <f>B14+C13</f>
-        <v>-626</v>
-      </c>
-      <c r="D14" s="37">
+        <v>7574</v>
+      </c>
+      <c r="D14" s="38">
         <f>C14+D13</f>
-        <v>5541</v>
-      </c>
-      <c r="E14" s="37">
+        <v>4841</v>
+      </c>
+      <c r="E14" s="38">
         <f>D14+E13</f>
-        <v>11708</v>
-      </c>
-      <c r="F14" s="37">
+        <v>23108</v>
+      </c>
+      <c r="F14" s="38">
         <f>E14+F13</f>
-        <v>17875</v>
-      </c>
-      <c r="G14" s="37">
+        <v>20375</v>
+      </c>
+      <c r="G14" s="38">
         <f>F14+G13</f>
-        <v>24042</v>
-      </c>
-      <c r="H14" s="37">
+        <v>17642</v>
+      </c>
+      <c r="H14" s="38">
         <f>G14+H13</f>
-        <v>30209</v>
-      </c>
-      <c r="I14" s="37">
+        <v>35909</v>
+      </c>
+      <c r="I14" s="38">
         <f>H14+I13</f>
-        <v>36376</v>
-      </c>
-      <c r="J14" s="37">
+        <v>33176</v>
+      </c>
+      <c r="J14" s="38">
         <f>I14+J13</f>
-        <v>42543</v>
-      </c>
-      <c r="K14" s="37">
+        <v>30443</v>
+      </c>
+      <c r="K14" s="38">
         <f>J14+K13</f>
         <v>48710</v>
       </c>
-      <c r="L14" s="37">
+      <c r="L14" s="38">
         <f>K14+L13</f>
         <v>61920</v>
       </c>
-      <c r="M14" s="37">
+      <c r="M14" s="38">
         <f>L14+M13</f>
         <v>62170</v>
       </c>
-      <c r="N14" s="32">
+      <c r="N14" s="33">
         <f>M14</f>
         <v>62170</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="B16" s="19"/>
       <c r="C16" s="19"/>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="B17" s="23">
         <v>0</v>
@@ -4373,25 +4434,25 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>299</v>
-      </c>
-      <c r="B18" s="37">
+        <v>312</v>
+      </c>
+      <c r="B18" s="38">
         <f>M14</f>
         <v>62170</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>300</v>
-      </c>
-      <c r="B19" s="38">
+        <v>313</v>
+      </c>
+      <c r="B19" s="25">
         <f>MIN(B14:M14)</f>
-        <v>-6793</v>
+        <v>4841</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -4401,7 +4462,7 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="39" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="B21" s="39"/>
       <c r="C21" s="39"/>
@@ -4430,7 +4491,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
@@ -4439,7 +4500,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -4449,7 +4510,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="40" t="s">
-        <v>304</v>
+        <v>317</v>
       </c>
       <c r="B2" s="40"/>
       <c r="C2" s="40"/>
@@ -4462,24 +4523,24 @@
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>248</v>
+        <v>261</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -4489,27 +4550,27 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="41" t="s">
-        <v>254</v>
-      </c>
-      <c r="B5" s="31">
+        <v>267</v>
+      </c>
+      <c r="B5" s="32">
         <v>184667</v>
       </c>
-      <c r="C5" s="31">
+      <c r="C5" s="32">
         <v>340512</v>
       </c>
-      <c r="D5" s="31">
+      <c r="D5" s="32">
         <v>427946</v>
       </c>
-      <c r="E5" s="31">
+      <c r="E5" s="32">
         <v>500518</v>
       </c>
-      <c r="F5" s="31">
+      <c r="F5" s="32">
         <v>516085</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="19" t="s">
-        <v>291</v>
+        <v>304</v>
       </c>
       <c r="B7" s="19"/>
       <c r="C7" s="19"/>
@@ -4519,211 +4580,231 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>292</v>
-      </c>
-      <c r="B8" s="33">
+        <v>305</v>
+      </c>
+      <c r="B8" s="34">
         <v>118934</v>
       </c>
-      <c r="C8" s="33">
+      <c r="C8" s="34">
         <v>147003</v>
       </c>
-      <c r="D8" s="33">
+      <c r="D8" s="34">
         <v>151413</v>
       </c>
-      <c r="E8" s="33">
+      <c r="E8" s="34">
         <v>155955</v>
       </c>
-      <c r="F8" s="33">
+      <c r="F8" s="34">
         <v>160634</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>293</v>
-      </c>
-      <c r="B9" s="33">
+        <v>306</v>
+      </c>
+      <c r="B9" s="34">
         <v>40500</v>
       </c>
-      <c r="C9" s="33">
+      <c r="C9" s="34">
         <v>55002</v>
       </c>
-      <c r="D9" s="33">
+      <c r="D9" s="34">
         <v>60047</v>
       </c>
-      <c r="E9" s="33">
+      <c r="E9" s="34">
         <v>64471</v>
       </c>
-      <c r="F9" s="33">
+      <c r="F9" s="34">
         <v>66405</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>305</v>
-      </c>
-      <c r="B10" s="33">
+        <v>318</v>
+      </c>
+      <c r="B10" s="34">
         <v>0</v>
       </c>
-      <c r="C10" s="33">
+      <c r="C10" s="34">
         <v>0</v>
       </c>
-      <c r="D10" s="33">
+      <c r="D10" s="34">
         <v>0</v>
       </c>
-      <c r="E10" s="33">
+      <c r="E10" s="34">
         <v>0</v>
       </c>
-      <c r="F10" s="33">
+      <c r="F10" s="34">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>306</v>
-      </c>
-      <c r="B11" s="33">
+        <v>319</v>
+      </c>
+      <c r="B11" s="34">
+        <v>0</v>
+      </c>
+      <c r="C11" s="34">
+        <v>0</v>
+      </c>
+      <c r="D11" s="34">
+        <v>0</v>
+      </c>
+      <c r="E11" s="34">
+        <v>0</v>
+      </c>
+      <c r="F11" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="10" t="s">
+        <v>320</v>
+      </c>
+      <c r="B12" s="34">
         <v>714</v>
       </c>
-      <c r="C11" s="33">
+      <c r="C12" s="34">
         <v>714</v>
       </c>
-      <c r="D11" s="33">
+      <c r="D12" s="34">
         <v>714</v>
       </c>
-      <c r="E11" s="33">
+      <c r="E12" s="34">
         <v>714</v>
       </c>
-      <c r="F11" s="33">
+      <c r="F12" s="34">
         <v>714</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="41" t="s">
-        <v>271</v>
-      </c>
-      <c r="B12" s="31">
-        <f>SUM(B8:B11)</f>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="41" t="s">
+        <v>284</v>
+      </c>
+      <c r="B13" s="32">
+        <f>SUM(B8:B12)</f>
         <v>160148</v>
       </c>
-      <c r="C12" s="31">
-        <f>SUM(C8:C11)</f>
+      <c r="C13" s="32">
+        <f>SUM(C8:C12)</f>
         <v>202719</v>
       </c>
-      <c r="D12" s="31">
-        <f>SUM(D8:D11)</f>
+      <c r="D13" s="32">
+        <f>SUM(D8:D12)</f>
         <v>212174</v>
       </c>
-      <c r="E12" s="31">
-        <f>SUM(E8:E11)</f>
+      <c r="E13" s="32">
+        <f>SUM(E8:E12)</f>
         <v>221140</v>
       </c>
-      <c r="F12" s="31">
-        <f>SUM(F8:F11)</f>
+      <c r="F13" s="32">
+        <f>SUM(F8:F12)</f>
         <v>227753</v>
       </c>
     </row>
-    <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="19" t="s">
-        <v>307</v>
-      </c>
-      <c r="B14" s="19"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="19"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="41" t="s">
-        <v>273</v>
-      </c>
-      <c r="B15" s="32">
-        <f>B5-B12</f>
+    <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="19" t="s">
+        <v>321</v>
+      </c>
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="41" t="s">
+        <v>286</v>
+      </c>
+      <c r="B16" s="33">
+        <f>B5-B13</f>
         <v>24518</v>
       </c>
-      <c r="C15" s="32">
-        <f>C5-C12</f>
+      <c r="C16" s="33">
+        <f>C5-C13</f>
         <v>137793</v>
       </c>
-      <c r="D15" s="32">
-        <f>D5-D12</f>
+      <c r="D16" s="33">
+        <f>D5-D13</f>
         <v>215772</v>
       </c>
-      <c r="E15" s="32">
-        <f>E5-E12</f>
+      <c r="E16" s="33">
+        <f>E5-E13</f>
         <v>279377</v>
       </c>
-      <c r="F15" s="32">
-        <f>F5-F12</f>
+      <c r="F16" s="33">
+        <f>F5-F13</f>
         <v>288332</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="11" t="s">
-        <v>274</v>
-      </c>
-      <c r="B16" s="29">
-        <f>IF(B5=0,0,B15/B5)</f>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="11" t="s">
+        <v>287</v>
+      </c>
+      <c r="B17" s="26">
+        <f>IF(B5=0,0,B16/B5)</f>
         <v>0.13277011</v>
       </c>
-      <c r="C16" s="29">
-        <f>IF(C5=0,0,C15/C5)</f>
+      <c r="C17" s="26">
+        <f>IF(C5=0,0,C16/C5)</f>
         <v>0.4046644</v>
       </c>
-      <c r="D16" s="29">
-        <f>IF(D5=0,0,D15/D5)</f>
+      <c r="D17" s="26">
+        <f>IF(D5=0,0,D16/D5)</f>
         <v>0.50420372</v>
       </c>
-      <c r="E16" s="29">
-        <f>IF(E5=0,0,E15/E5)</f>
+      <c r="E17" s="26">
+        <f>IF(E5=0,0,E16/E5)</f>
         <v>0.55817675</v>
       </c>
-      <c r="F16" s="29">
-        <f>IF(F5=0,0,F15/F5)</f>
+      <c r="F17" s="26">
+        <f>IF(F5=0,0,F16/F5)</f>
         <v>0.55869082</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="10" t="s">
-        <v>275</v>
-      </c>
-      <c r="B17" s="33">
-        <f>B15</f>
-        <v>24518</v>
-      </c>
-      <c r="C17" s="33">
-        <f>B17+C15</f>
-        <v>162311</v>
-      </c>
-      <c r="D17" s="33">
-        <f>C17+D15</f>
-        <v>378083</v>
-      </c>
-      <c r="E17" s="33">
-        <f>D17+E15</f>
-        <v>657460</v>
-      </c>
-      <c r="F17" s="33">
-        <f>E17+F15</f>
-        <v>945792</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
-        <v>308</v>
-      </c>
-      <c r="B18" s="42" t="s">
-        <v>309</v>
-      </c>
-      <c r="C18" s="43" t="s">
+        <v>288</v>
+      </c>
+      <c r="B18" s="34">
+        <f>B16</f>
+        <v>24518</v>
+      </c>
+      <c r="C18" s="34">
+        <f>B18+C16</f>
+        <v>162311</v>
+      </c>
+      <c r="D18" s="34">
+        <f>C18+D16</f>
+        <v>378083</v>
+      </c>
+      <c r="E18" s="34">
+        <f>D18+E16</f>
+        <v>657460</v>
+      </c>
+      <c r="F18" s="34">
+        <f>E18+F16</f>
+        <v>945792</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="10" t="s">
+        <v>322</v>
+      </c>
+      <c r="B19" s="42" t="s">
+        <v>323</v>
+      </c>
+      <c r="C19" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="D18" s="43" t="s">
+      <c r="D19" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E18" s="43" t="s">
+      <c r="E19" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="F18" s="43" t="s">
+      <c r="F19" s="43" t="s">
         <v>7</v>
       </c>
     </row>
@@ -4767,24 +4848,24 @@
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>310</v>
+        <v>324</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -4794,19 +4875,19 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="44" t="s">
-        <v>311</v>
+        <v>325</v>
       </c>
       <c r="B5" s="45" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="C5" s="46" t="s">
-        <v>312</v>
+        <v>326</v>
       </c>
       <c r="D5" s="44" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="E5" s="45" t="s">
-        <v>233</v>
+        <v>246</v>
       </c>
     </row>
   </sheetData>
@@ -4835,7 +4916,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>314</v>
+        <v>328</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -4848,24 +4929,24 @@
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>315</v>
+        <v>329</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -4875,117 +4956,117 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>316</v>
+        <v>330</v>
       </c>
       <c r="B5" s="47">
         <f>'Monthly Cash Flow Y1'!M14</f>
         <v>62170</v>
       </c>
       <c r="C5" s="47">
-        <f>B5+'5-Year Operating Stmt'!C15</f>
+        <f>B5+'5-Year Operating Stmt'!C16</f>
         <v>200677</v>
       </c>
       <c r="D5" s="47">
-        <f>B5+'5-Year Operating Stmt'!C15+'5-Year Operating Stmt'!D15</f>
+        <f>B5+'5-Year Operating Stmt'!C16+'5-Year Operating Stmt'!D16</f>
         <v>417164</v>
       </c>
       <c r="E5" s="47">
-        <f>B5+'5-Year Operating Stmt'!C15+'5-Year Operating Stmt'!D15+'5-Year Operating Stmt'!E15</f>
+        <f>B5+'5-Year Operating Stmt'!C16+'5-Year Operating Stmt'!D16+'5-Year Operating Stmt'!E16</f>
         <v>697255</v>
       </c>
       <c r="F5" s="47">
-        <f>B5+'5-Year Operating Stmt'!C15+'5-Year Operating Stmt'!D15+'5-Year Operating Stmt'!E15+'5-Year Operating Stmt'!F15</f>
+        <f>B5+'5-Year Operating Stmt'!C16+'5-Year Operating Stmt'!D16+'5-Year Operating Stmt'!E16+'5-Year Operating Stmt'!F16</f>
         <v>986301</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>317</v>
-      </c>
-      <c r="B6" s="30">
+        <v>331</v>
+      </c>
+      <c r="B6" s="25">
         <v>1007</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="25">
         <v>1036</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="25">
         <v>1067</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="25">
         <v>1098</v>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="25">
         <v>1131</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>318</v>
-      </c>
-      <c r="B7" s="30">
+        <v>332</v>
+      </c>
+      <c r="B7" s="25">
         <v>4286</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="25">
         <v>3571</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="25">
         <v>2857</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="25">
         <v>2143</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="25">
         <v>1429</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>319</v>
-      </c>
-      <c r="B8" s="30">
+        <v>333</v>
+      </c>
+      <c r="B8" s="25">
         <v>0</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="25">
         <v>0</v>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="25">
         <v>0</v>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="25">
         <v>0</v>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="25">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>320</v>
-      </c>
-      <c r="B9" s="31">
+        <v>334</v>
+      </c>
+      <c r="B9" s="32">
         <f>SUM(B5:B8)</f>
         <v>67463</v>
       </c>
-      <c r="C9" s="31">
+      <c r="C9" s="32">
         <f>SUM(C5:C8)</f>
         <v>205285</v>
       </c>
-      <c r="D9" s="31">
+      <c r="D9" s="32">
         <f>SUM(D5:D8)</f>
         <v>421088</v>
       </c>
-      <c r="E9" s="31">
+      <c r="E9" s="32">
         <f>SUM(E5:E8)</f>
         <v>700496</v>
       </c>
-      <c r="F9" s="31">
+      <c r="F9" s="32">
         <f>SUM(F5:F8)</f>
         <v>988860</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>321</v>
+        <v>335</v>
       </c>
       <c r="B11" s="19"/>
       <c r="C11" s="19"/>
@@ -4995,72 +5076,72 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>322</v>
-      </c>
-      <c r="B12" s="30">
+        <v>336</v>
+      </c>
+      <c r="B12" s="25">
         <v>0</v>
       </c>
-      <c r="C12" s="30">
+      <c r="C12" s="25">
         <v>0</v>
       </c>
-      <c r="D12" s="30">
+      <c r="D12" s="25">
         <v>0</v>
       </c>
-      <c r="E12" s="30">
+      <c r="E12" s="25">
         <v>0</v>
       </c>
-      <c r="F12" s="30">
+      <c r="F12" s="25">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>323</v>
-      </c>
-      <c r="B13" s="30">
+        <v>337</v>
+      </c>
+      <c r="B13" s="25">
         <v>0</v>
       </c>
-      <c r="C13" s="30">
+      <c r="C13" s="25">
         <v>0</v>
       </c>
-      <c r="D13" s="30">
+      <c r="D13" s="25">
         <v>0</v>
       </c>
-      <c r="E13" s="30">
+      <c r="E13" s="25">
         <v>0</v>
       </c>
-      <c r="F13" s="30">
+      <c r="F13" s="25">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>324</v>
-      </c>
-      <c r="B14" s="31" t="str">
+        <v>338</v>
+      </c>
+      <c r="B14" s="32" t="str">
         <f>SUM(B12:B13)</f>
         <v>0</v>
       </c>
-      <c r="C14" s="31" t="str">
+      <c r="C14" s="32" t="str">
         <f>SUM(C12:C13)</f>
         <v>0</v>
       </c>
-      <c r="D14" s="31" t="str">
+      <c r="D14" s="32" t="str">
         <f>SUM(D12:D13)</f>
         <v>0</v>
       </c>
-      <c r="E14" s="31" t="str">
+      <c r="E14" s="32" t="str">
         <f>SUM(E12:E13)</f>
         <v>0</v>
       </c>
-      <c r="F14" s="31" t="str">
+      <c r="F14" s="32" t="str">
         <f>SUM(F12:F13)</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
-        <v>325</v>
+        <v>339</v>
       </c>
       <c r="B16" s="19"/>
       <c r="C16" s="19"/>
@@ -5070,32 +5151,32 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>326</v>
-      </c>
-      <c r="B17" s="32">
+        <v>340</v>
+      </c>
+      <c r="B17" s="33">
         <f>B9-B14</f>
         <v>67463</v>
       </c>
-      <c r="C17" s="32">
+      <c r="C17" s="33">
         <f>C9-C14</f>
         <v>205285</v>
       </c>
-      <c r="D17" s="32">
+      <c r="D17" s="33">
         <f>D9-D14</f>
         <v>421088</v>
       </c>
-      <c r="E17" s="32">
+      <c r="E17" s="33">
         <f>E9-E14</f>
         <v>700496</v>
       </c>
-      <c r="F17" s="32">
+      <c r="F17" s="33">
         <f>F9-F14</f>
         <v>988860</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="B19" s="48" t="str">
         <f>B9-B14-B17</f>
@@ -5135,7 +5216,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
@@ -5144,7 +5225,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>328</v>
+        <v>342</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -5157,24 +5238,24 @@
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>329</v>
+        <v>343</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -5184,172 +5265,172 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>330</v>
-      </c>
-      <c r="B5" s="30">
+        <v>344</v>
+      </c>
+      <c r="B5" s="25">
         <v>184667</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="25">
         <v>340512</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="25">
         <v>427946</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="25">
         <v>500518</v>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="25">
         <v>516085</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>292</v>
-      </c>
-      <c r="B6" s="30">
+        <v>305</v>
+      </c>
+      <c r="B6" s="25">
         <v>118934</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="25">
         <v>147003</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="25">
         <v>151413</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="25">
         <v>155955</v>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="25">
         <v>160634</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>293</v>
-      </c>
-      <c r="B7" s="30">
+        <v>306</v>
+      </c>
+      <c r="B7" s="25">
         <v>40500</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="25">
         <v>55002</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="25">
         <v>60047</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="25">
         <v>64471</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="25">
         <v>66405</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>273</v>
-      </c>
-      <c r="B8" s="33">
+        <v>286</v>
+      </c>
+      <c r="B8" s="34">
         <v>25232</v>
       </c>
-      <c r="C8" s="33">
+      <c r="C8" s="34">
         <v>138507</v>
       </c>
-      <c r="D8" s="33">
+      <c r="D8" s="34">
         <v>216486</v>
       </c>
-      <c r="E8" s="33">
+      <c r="E8" s="34">
         <v>280092</v>
       </c>
-      <c r="F8" s="33">
+      <c r="F8" s="34">
         <v>289046</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>331</v>
-      </c>
-      <c r="B9" s="30">
+        <v>345</v>
+      </c>
+      <c r="B9" s="25">
         <v>714</v>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="25">
         <v>714</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="25">
         <v>714</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="25">
         <v>714</v>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="25">
         <v>714</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>332</v>
-      </c>
-      <c r="B10" s="30">
+        <v>346</v>
+      </c>
+      <c r="B10" s="25">
         <v>0</v>
       </c>
-      <c r="C10" s="30">
+      <c r="C10" s="25">
         <v>0</v>
       </c>
-      <c r="D10" s="30">
+      <c r="D10" s="25">
         <v>0</v>
       </c>
-      <c r="E10" s="30">
+      <c r="E10" s="25">
         <v>0</v>
       </c>
-      <c r="F10" s="30">
+      <c r="F10" s="25">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>333</v>
-      </c>
-      <c r="B11" s="33">
+        <v>347</v>
+      </c>
+      <c r="B11" s="34">
         <f>B8+B9+B10</f>
         <v>25947</v>
       </c>
-      <c r="C11" s="33">
+      <c r="C11" s="34">
         <f>C8+C9+C10</f>
         <v>139222</v>
       </c>
-      <c r="D11" s="33">
+      <c r="D11" s="34">
         <f>D8+D9+D10</f>
         <v>217200</v>
       </c>
-      <c r="E11" s="33">
+      <c r="E11" s="34">
         <f>E8+E9+E10</f>
         <v>280806</v>
       </c>
-      <c r="F11" s="33">
+      <c r="F11" s="34">
         <f>F8+F9+F10</f>
         <v>289761</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>334</v>
+        <v>348</v>
       </c>
       <c r="B12" s="49" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
       <c r="C12" s="49" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
       <c r="D12" s="49" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
       <c r="E12" s="49" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
       <c r="F12" s="49" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="19" t="s">
-        <v>336</v>
+        <v>350</v>
       </c>
       <c r="B14" s="19"/>
       <c r="C14" s="19"/>
@@ -5359,312 +5440,332 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>337</v>
-      </c>
-      <c r="B15" s="30">
+        <v>351</v>
+      </c>
+      <c r="B15" s="25">
+        <v>40232</v>
+      </c>
+      <c r="C15" s="25">
+        <v>178740</v>
+      </c>
+      <c r="D15" s="25">
+        <v>395226</v>
+      </c>
+      <c r="E15" s="25">
+        <v>675318</v>
+      </c>
+      <c r="F15" s="25">
+        <v>964364</v>
+      </c>
+    </row>
+    <row r="16" hidden="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="11" t="s">
+        <v>352</v>
+      </c>
+      <c r="B16" s="25">
         <v>62170</v>
       </c>
-      <c r="C15" s="30">
+      <c r="C16" s="25">
         <v>200677</v>
       </c>
-      <c r="D15" s="30">
+      <c r="D16" s="25">
         <v>417164</v>
       </c>
-      <c r="E15" s="30">
+      <c r="E16" s="25">
         <v>697255</v>
       </c>
-      <c r="F15" s="30">
+      <c r="F16" s="25">
         <v>986301</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="11" t="s">
-        <v>338</v>
-      </c>
-      <c r="B16" s="50">
-        <f>IF((B5-B8)=0,0,(B15/(B5-B8))*365)</f>
-        <v>142</v>
-      </c>
-      <c r="C16" s="50">
-        <f>IF((C5-C8)=0,0,(C15/(C5-C8))*365)</f>
-        <v>363</v>
-      </c>
-      <c r="D16" s="50">
-        <f>IF((D5-D8)=0,0,(D15/(D5-D8))*365)</f>
-        <v>720</v>
-      </c>
-      <c r="E16" s="50">
-        <f>IF((E5-E8)=0,0,(E15/(E5-E8))*365)</f>
-        <v>1155</v>
-      </c>
-      <c r="F16" s="50">
-        <f>IF((F5-F8)=0,0,(F15/(F5-F8))*365)</f>
-        <v>1586</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>339</v>
-      </c>
-      <c r="B17" s="34">
-        <f>IF((B5-B8)=0,0,B15/((B5-B8)/12))</f>
-        <v>4.7</v>
-      </c>
-      <c r="C17" s="34">
-        <f>IF((C5-C8)=0,0,C15/((C5-C8)/12))</f>
-        <v>11.9</v>
-      </c>
-      <c r="D17" s="34">
-        <f>IF((D5-D8)=0,0,D15/((D5-D8)/12))</f>
-        <v>23.7</v>
-      </c>
-      <c r="E17" s="34">
-        <f>IF((E5-E8)=0,0,E15/((E5-E8)/12))</f>
-        <v>38</v>
-      </c>
-      <c r="F17" s="34">
-        <f>IF((F5-F8)=0,0,F15/((F5-F8)/12))</f>
-        <v>52.1</v>
+        <v>353</v>
+      </c>
+      <c r="B17" s="50">
+        <f>IF((B5-B8)=0,0,(B16/(B5-B8))*365)</f>
+        <v>142</v>
+      </c>
+      <c r="C17" s="50">
+        <f>IF((C5-C8)=0,0,(C16/(C5-C8))*365)</f>
+        <v>363</v>
+      </c>
+      <c r="D17" s="50">
+        <f>IF((D5-D8)=0,0,(D16/(D5-D8))*365)</f>
+        <v>720</v>
+      </c>
+      <c r="E17" s="50">
+        <f>IF((E5-E8)=0,0,(E16/(E5-E8))*365)</f>
+        <v>1155</v>
+      </c>
+      <c r="F17" s="50">
+        <f>IF((F5-F8)=0,0,(F16/(F5-F8))*365)</f>
+        <v>1586</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="B18" s="29">
+        <v>354</v>
+      </c>
+      <c r="B18" s="35">
+        <f>IF((B5-B8)=0,0,B16/((B5-B8)/12))</f>
+        <v>4.7</v>
+      </c>
+      <c r="C18" s="35">
+        <f>IF((C5-C8)=0,0,C16/((C5-C8)/12))</f>
+        <v>11.9</v>
+      </c>
+      <c r="D18" s="35">
+        <f>IF((D5-D8)=0,0,D16/((D5-D8)/12))</f>
+        <v>23.7</v>
+      </c>
+      <c r="E18" s="35">
+        <f>IF((E5-E8)=0,0,E16/((E5-E8)/12))</f>
+        <v>38</v>
+      </c>
+      <c r="F18" s="35">
+        <f>IF((F5-F8)=0,0,F16/((F5-F8)/12))</f>
+        <v>52.1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="11" t="s">
+        <v>214</v>
+      </c>
+      <c r="B19" s="26">
         <v>0.48</v>
       </c>
-      <c r="C18" s="29">
+      <c r="C19" s="26">
         <v>0.72</v>
       </c>
-      <c r="D18" s="29">
+      <c r="D19" s="26">
         <v>0.88</v>
       </c>
-      <c r="E18" s="29">
+      <c r="E19" s="26">
         <v>1</v>
       </c>
-      <c r="F18" s="29">
+      <c r="F19" s="26">
         <v>1</v>
       </c>
     </row>
-    <row r="20" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="19" t="s">
-        <v>340</v>
-      </c>
-      <c r="B20" s="19"/>
-      <c r="C20" s="19"/>
-      <c r="D20" s="19"/>
-      <c r="E20" s="19"/>
-      <c r="F20" s="19"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="11" t="s">
-        <v>239</v>
-      </c>
-      <c r="B21" s="30">
-        <v>15389</v>
-      </c>
-      <c r="C21" s="30">
-        <v>18917</v>
-      </c>
-      <c r="D21" s="30">
-        <v>19452</v>
-      </c>
-      <c r="E21" s="30">
-        <v>20021</v>
-      </c>
-      <c r="F21" s="30">
-        <v>20643</v>
-      </c>
+    <row r="21" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="19" t="s">
+        <v>355</v>
+      </c>
+      <c r="B21" s="19"/>
+      <c r="C21" s="19"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="19"/>
+      <c r="F21" s="19"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>341</v>
-      </c>
-      <c r="B22" s="30">
-        <v>118934</v>
-      </c>
-      <c r="C22" s="30">
-        <v>147003</v>
-      </c>
-      <c r="D22" s="30">
-        <v>151413</v>
-      </c>
-      <c r="E22" s="30">
-        <v>155955</v>
-      </c>
-      <c r="F22" s="30">
-        <v>160634</v>
+        <v>252</v>
+      </c>
+      <c r="B22" s="25">
+        <v>15389</v>
+      </c>
+      <c r="C22" s="25">
+        <v>18917</v>
+      </c>
+      <c r="D22" s="25">
+        <v>19452</v>
+      </c>
+      <c r="E22" s="25">
+        <v>20021</v>
+      </c>
+      <c r="F22" s="25">
+        <v>20643</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
-        <v>342</v>
-      </c>
-      <c r="B23" s="30">
+        <v>356</v>
+      </c>
+      <c r="B23" s="25">
+        <v>118934</v>
+      </c>
+      <c r="C23" s="25">
+        <v>147003</v>
+      </c>
+      <c r="D23" s="25">
+        <v>151413</v>
+      </c>
+      <c r="E23" s="25">
+        <v>155955</v>
+      </c>
+      <c r="F23" s="25">
+        <v>160634</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="11" t="s">
+        <v>357</v>
+      </c>
+      <c r="B24" s="25">
         <v>3375</v>
       </c>
-      <c r="C23" s="30">
+      <c r="C24" s="25">
         <v>3056</v>
       </c>
-      <c r="D23" s="30">
+      <c r="D24" s="25">
         <v>2729</v>
       </c>
-      <c r="E23" s="30">
+      <c r="E24" s="25">
         <v>2579</v>
       </c>
-      <c r="F23" s="30">
+      <c r="F24" s="25">
         <v>2656</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="10" t="s">
-        <v>343</v>
-      </c>
-      <c r="B24" s="51">
-        <v>10</v>
-      </c>
-      <c r="C24" s="51">
-        <v>10</v>
-      </c>
-      <c r="D24" s="51">
-        <v>10</v>
-      </c>
-      <c r="E24" s="51">
-        <v>9</v>
-      </c>
-      <c r="F24" s="51">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="26" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="19" t="s">
-        <v>344</v>
-      </c>
-      <c r="B26" s="19"/>
-      <c r="C26" s="19"/>
-      <c r="D26" s="19"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="19"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="11" t="s">
-        <v>345</v>
-      </c>
-      <c r="B27" s="52" t="s">
-        <v>335</v>
-      </c>
-      <c r="C27" s="52" t="s">
-        <v>335</v>
-      </c>
-      <c r="D27" s="52" t="s">
-        <v>335</v>
-      </c>
-      <c r="E27" s="52" t="s">
-        <v>335</v>
-      </c>
-      <c r="F27" s="52" t="s">
-        <v>335</v>
-      </c>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="B25" s="51">
+        <v>11</v>
+      </c>
+      <c r="C25" s="51">
+        <v>11</v>
+      </c>
+      <c r="D25" s="51">
+        <v>11</v>
+      </c>
+      <c r="E25" s="51">
+        <v>11</v>
+      </c>
+      <c r="F25" s="51">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="19" t="s">
+        <v>359</v>
+      </c>
+      <c r="B27" s="19"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
-        <v>346</v>
-      </c>
-      <c r="B28" s="53" t="s">
-        <v>347</v>
-      </c>
-      <c r="C28" s="53" t="s">
-        <v>347</v>
-      </c>
-      <c r="D28" s="53" t="s">
-        <v>347</v>
-      </c>
-      <c r="E28" s="53" t="s">
-        <v>347</v>
-      </c>
-      <c r="F28" s="53" t="s">
-        <v>347</v>
+        <v>360</v>
+      </c>
+      <c r="B28" s="52" t="s">
+        <v>349</v>
+      </c>
+      <c r="C28" s="52" t="s">
+        <v>349</v>
+      </c>
+      <c r="D28" s="52" t="s">
+        <v>349</v>
+      </c>
+      <c r="E28" s="52" t="s">
+        <v>349</v>
+      </c>
+      <c r="F28" s="52" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
-        <v>348</v>
-      </c>
-      <c r="B29" s="52" t="s">
-        <v>335</v>
-      </c>
-      <c r="C29" s="52" t="s">
-        <v>335</v>
-      </c>
-      <c r="D29" s="52" t="s">
-        <v>335</v>
-      </c>
-      <c r="E29" s="52" t="s">
-        <v>335</v>
-      </c>
-      <c r="F29" s="52" t="s">
-        <v>335</v>
+        <v>361</v>
+      </c>
+      <c r="B29" s="53" t="s">
+        <v>362</v>
+      </c>
+      <c r="C29" s="53" t="s">
+        <v>362</v>
+      </c>
+      <c r="D29" s="53" t="s">
+        <v>362</v>
+      </c>
+      <c r="E29" s="53" t="s">
+        <v>362</v>
+      </c>
+      <c r="F29" s="53" t="s">
+        <v>362</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
+        <v>363</v>
+      </c>
+      <c r="B30" s="52" t="s">
         <v>349</v>
       </c>
-      <c r="B30" s="54" t="s">
-        <v>350</v>
-      </c>
-      <c r="C30" s="53" t="s">
-        <v>347</v>
-      </c>
-      <c r="D30" s="53" t="s">
-        <v>347</v>
-      </c>
-      <c r="E30" s="53" t="s">
-        <v>347</v>
-      </c>
-      <c r="F30" s="53" t="s">
-        <v>347</v>
+      <c r="C30" s="52" t="s">
+        <v>349</v>
+      </c>
+      <c r="D30" s="52" t="s">
+        <v>349</v>
+      </c>
+      <c r="E30" s="52" t="s">
+        <v>349</v>
+      </c>
+      <c r="F30" s="52" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
-        <v>351</v>
-      </c>
-      <c r="B31" s="53" t="s">
-        <v>347</v>
+        <v>364</v>
+      </c>
+      <c r="B31" s="54" t="s">
+        <v>365</v>
       </c>
       <c r="C31" s="53" t="s">
-        <v>347</v>
+        <v>362</v>
       </c>
       <c r="D31" s="53" t="s">
-        <v>347</v>
+        <v>362</v>
       </c>
       <c r="E31" s="53" t="s">
-        <v>347</v>
+        <v>362</v>
       </c>
       <c r="F31" s="53" t="s">
-        <v>347</v>
+        <v>362</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="11" t="s">
-        <v>352</v>
+        <v>366</v>
       </c>
       <c r="B32" s="53" t="s">
-        <v>347</v>
+        <v>362</v>
       </c>
       <c r="C32" s="53" t="s">
-        <v>347</v>
+        <v>362</v>
       </c>
       <c r="D32" s="53" t="s">
-        <v>347</v>
+        <v>362</v>
       </c>
       <c r="E32" s="53" t="s">
-        <v>347</v>
+        <v>362</v>
       </c>
       <c r="F32" s="53" t="s">
-        <v>347</v>
+        <v>362</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="11" t="s">
+        <v>367</v>
+      </c>
+      <c r="B33" s="53" t="s">
+        <v>362</v>
+      </c>
+      <c r="C33" s="53" t="s">
+        <v>362</v>
+      </c>
+      <c r="D33" s="53" t="s">
+        <v>362</v>
+      </c>
+      <c r="E33" s="53" t="s">
+        <v>362</v>
+      </c>
+      <c r="F33" s="53" t="s">
+        <v>362</v>
       </c>
     </row>
   </sheetData>
@@ -5705,57 +5806,57 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="55" t="s">
-        <v>353</v>
+        <v>368</v>
       </c>
       <c r="B3" s="55" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D3" s="55" t="s">
-        <v>354</v>
+        <v>369</v>
       </c>
       <c r="E3" s="55" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>355</v>
-      </c>
-      <c r="B4" s="30">
+        <v>370</v>
+      </c>
+      <c r="B4" s="25">
         <v>20000</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>356</v>
-      </c>
-      <c r="E4" s="30">
+        <v>371</v>
+      </c>
+      <c r="E4" s="25">
         <v>15000</v>
       </c>
     </row>
     <row r="5" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D5" s="11" t="s">
-        <v>357</v>
-      </c>
-      <c r="E5" s="30">
+        <v>372</v>
+      </c>
+      <c r="E5" s="25">
         <v>5000</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>358</v>
-      </c>
-      <c r="B7" s="32">
+        <v>373</v>
+      </c>
+      <c r="B7" s="33">
         <v>20000</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>359</v>
-      </c>
-      <c r="E7" s="32">
+        <v>374</v>
+      </c>
+      <c r="E7" s="33">
         <v>20000</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>360</v>
+        <v>375</v>
       </c>
       <c r="B8" s="48">
         <v>0</v>
@@ -5778,7 +5879,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B3:C44"/>
+  <dimension ref="B3:C45"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -6052,18 +6153,26 @@
         <v>93</v>
       </c>
     </row>
-    <row r="44" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B44" s="14" t="s">
+    <row r="42" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B42" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="C44" s="14"/>
+      <c r="C42" s="13" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="45" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B45" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="C45" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B45:C45"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C19" r:id="rId1" location="#'Instructions'!A1"/>
@@ -6086,9 +6195,10 @@
     <hyperlink ref="C36" r:id="rId18" location="#'DSCR &amp; Covenants'!A1"/>
     <hyperlink ref="C37" r:id="rId19" location="#'Sources &amp; Uses'!A1"/>
     <hyperlink ref="C38" r:id="rId20" location="#'Scenarios'!A1"/>
-    <hyperlink ref="C39" r:id="rId21" location="#'Underwriting Snapshot'!A1"/>
+    <hyperlink ref="C39" r:id="rId21" location="#'Lender Snapshot'!A1"/>
     <hyperlink ref="C40" r:id="rId22" location="#'Financial Health'!A1"/>
     <hyperlink ref="C41" r:id="rId23" location="#'Budget Narrative'!A1"/>
+    <hyperlink ref="C42" r:id="rId24" location="#'Assumptions Confidence'!A1"/>
   </hyperlinks>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -6112,7 +6222,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>361</v>
+        <v>376</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -6122,7 +6232,7 @@
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>362</v>
+        <v>377</v>
       </c>
       <c r="B3" s="19"/>
       <c r="C3" s="19"/>
@@ -6132,7 +6242,7 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
-        <v>363</v>
+        <v>378</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6140,124 +6250,124 @@
         <v>7</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E5" s="21" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F5" s="21" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>330</v>
-      </c>
-      <c r="B6" s="30">
+        <v>344</v>
+      </c>
+      <c r="B6" s="25">
         <v>184667</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="25">
         <v>340512</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="25">
         <v>427946</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="25">
         <v>500518</v>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="25">
         <v>516085</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>271</v>
-      </c>
-      <c r="B7" s="30">
+        <v>284</v>
+      </c>
+      <c r="B7" s="25">
         <v>159434</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="25">
         <v>202005</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="25">
         <v>211460</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="25">
         <v>220426</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="25">
         <v>227039</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>273</v>
-      </c>
-      <c r="B8" s="32">
+        <v>286</v>
+      </c>
+      <c r="B8" s="33">
         <v>25232</v>
       </c>
-      <c r="C8" s="32">
+      <c r="C8" s="33">
         <v>138507</v>
       </c>
-      <c r="D8" s="32">
+      <c r="D8" s="33">
         <v>216486</v>
       </c>
-      <c r="E8" s="32">
+      <c r="E8" s="33">
         <v>280092</v>
       </c>
-      <c r="F8" s="32">
+      <c r="F8" s="33">
         <v>289046</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>274</v>
-      </c>
-      <c r="B9" s="29">
+        <v>287</v>
+      </c>
+      <c r="B9" s="26">
         <v>0.13663808664259913</v>
       </c>
-      <c r="C9" s="29">
+      <c r="C9" s="26">
         <v>0.4067620818062212</v>
       </c>
-      <c r="D9" s="29">
+      <c r="D9" s="26">
         <v>0.5058728257176494</v>
       </c>
-      <c r="E9" s="29">
+      <c r="E9" s="26">
         <v>0.5596038436877832</v>
       </c>
-      <c r="F9" s="29">
+      <c r="F9" s="26">
         <v>0.5600748662293807</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>334</v>
+        <v>348</v>
       </c>
       <c r="B10" s="56" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
       <c r="C10" s="56" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
       <c r="D10" s="56" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
       <c r="E10" s="56" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
       <c r="F10" s="56" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>343</v>
+        <v>358</v>
       </c>
       <c r="B11" s="50">
         <v>10</v>
@@ -6277,7 +6387,7 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
-        <v>364</v>
+        <v>379</v>
       </c>
       <c r="B13" s="19"/>
       <c r="C13" s="19"/>
@@ -6287,7 +6397,7 @@
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
-        <v>365</v>
+        <v>380</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6295,124 +6405,124 @@
         <v>7</v>
       </c>
       <c r="B15" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C15" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E15" s="21" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F15" s="21" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>330</v>
-      </c>
-      <c r="B16" s="30">
+        <v>344</v>
+      </c>
+      <c r="B16" s="25">
         <v>147733</v>
       </c>
-      <c r="C16" s="30">
+      <c r="C16" s="25">
         <v>272410</v>
       </c>
-      <c r="D16" s="30">
+      <c r="D16" s="25">
         <v>342357</v>
       </c>
-      <c r="E16" s="30">
+      <c r="E16" s="25">
         <v>400414</v>
       </c>
-      <c r="F16" s="30">
+      <c r="F16" s="25">
         <v>412868</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>271</v>
-      </c>
-      <c r="B17" s="30">
+        <v>284</v>
+      </c>
+      <c r="B17" s="25">
         <v>159434</v>
       </c>
-      <c r="C17" s="30">
+      <c r="C17" s="25">
         <v>202005</v>
       </c>
-      <c r="D17" s="30">
+      <c r="D17" s="25">
         <v>211460</v>
       </c>
-      <c r="E17" s="30">
+      <c r="E17" s="25">
         <v>220426</v>
       </c>
-      <c r="F17" s="30">
+      <c r="F17" s="25">
         <v>227039</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
-        <v>273</v>
-      </c>
-      <c r="B18" s="32">
+        <v>286</v>
+      </c>
+      <c r="B18" s="33">
         <v>-11701</v>
       </c>
-      <c r="C18" s="32">
+      <c r="C18" s="33">
         <v>70405</v>
       </c>
-      <c r="D18" s="32">
+      <c r="D18" s="33">
         <v>130897</v>
       </c>
-      <c r="E18" s="32">
+      <c r="E18" s="33">
         <v>179988</v>
       </c>
-      <c r="F18" s="32">
+      <c r="F18" s="33">
         <v>185829</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>274</v>
-      </c>
-      <c r="B19" s="29">
+        <v>287</v>
+      </c>
+      <c r="B19" s="26">
         <v>-0.07920239169675096</v>
       </c>
-      <c r="C19" s="29">
+      <c r="C19" s="26">
         <v>0.2584526022577766</v>
       </c>
-      <c r="D19" s="29">
+      <c r="D19" s="26">
         <v>0.3823410321470617</v>
       </c>
-      <c r="E19" s="29">
+      <c r="E19" s="26">
         <v>0.4495048046097289</v>
       </c>
-      <c r="F19" s="29">
+      <c r="F19" s="26">
         <v>0.45009358278672595</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>334</v>
+        <v>348</v>
       </c>
       <c r="B20" s="56" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
       <c r="C20" s="56" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
       <c r="D20" s="56" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
       <c r="E20" s="56" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
       <c r="F20" s="56" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>343</v>
+        <v>358</v>
       </c>
       <c r="B21" s="50">
         <v>12</v>
@@ -6447,7 +6557,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -6458,7 +6568,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>366</v>
+        <v>381</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -6470,7 +6580,7 @@
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B3" s="19"/>
     </row>
@@ -6484,7 +6594,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>34</v>
@@ -6492,7 +6602,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>367</v>
+        <v>382</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>36</v>
@@ -6516,7 +6626,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>368</v>
+        <v>383</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>46</v>
@@ -6524,7 +6634,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>369</v>
+        <v>384</v>
       </c>
       <c r="B11" s="19"/>
       <c r="C11" s="19"/>
@@ -6545,124 +6655,124 @@
         <v>7</v>
       </c>
       <c r="D12" s="57" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E12" s="57" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F12" s="57" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G12" s="57" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="H12" s="57" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>330</v>
-      </c>
-      <c r="D13" s="30">
+        <v>344</v>
+      </c>
+      <c r="D13" s="25">
         <v>184667</v>
       </c>
-      <c r="E13" s="30">
+      <c r="E13" s="25">
         <v>340512</v>
       </c>
-      <c r="F13" s="30">
+      <c r="F13" s="25">
         <v>427946</v>
       </c>
-      <c r="G13" s="30">
+      <c r="G13" s="25">
         <v>500518</v>
       </c>
-      <c r="H13" s="30">
+      <c r="H13" s="25">
         <v>516085</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>271</v>
-      </c>
-      <c r="D14" s="30">
+        <v>284</v>
+      </c>
+      <c r="D14" s="25">
         <v>159434</v>
       </c>
-      <c r="E14" s="30">
+      <c r="E14" s="25">
         <v>202005</v>
       </c>
-      <c r="F14" s="30">
+      <c r="F14" s="25">
         <v>211460</v>
       </c>
-      <c r="G14" s="30">
+      <c r="G14" s="25">
         <v>220426</v>
       </c>
-      <c r="H14" s="30">
+      <c r="H14" s="25">
         <v>227039</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>273</v>
-      </c>
-      <c r="D15" s="30">
+        <v>286</v>
+      </c>
+      <c r="D15" s="25">
         <v>25232</v>
       </c>
-      <c r="E15" s="30">
+      <c r="E15" s="25">
         <v>138507</v>
       </c>
-      <c r="F15" s="30">
+      <c r="F15" s="25">
         <v>216486</v>
       </c>
-      <c r="G15" s="30">
+      <c r="G15" s="25">
         <v>280092</v>
       </c>
-      <c r="H15" s="30">
+      <c r="H15" s="25">
         <v>289046</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>370</v>
-      </c>
-      <c r="D16" s="30">
+        <v>385</v>
+      </c>
+      <c r="D16" s="25">
         <v>62170</v>
       </c>
-      <c r="E16" s="30">
+      <c r="E16" s="25">
         <v>200677</v>
       </c>
-      <c r="F16" s="30">
+      <c r="F16" s="25">
         <v>417164</v>
       </c>
-      <c r="G16" s="30">
+      <c r="G16" s="25">
         <v>697255</v>
       </c>
-      <c r="H16" s="30">
+      <c r="H16" s="25">
         <v>986301</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>371</v>
-      </c>
-      <c r="D17" s="30">
+        <v>386</v>
+      </c>
+      <c r="D17" s="25">
         <v>0</v>
       </c>
-      <c r="E17" s="30">
+      <c r="E17" s="25">
         <v>0</v>
       </c>
-      <c r="F17" s="30">
+      <c r="F17" s="25">
         <v>0</v>
       </c>
-      <c r="G17" s="30">
+      <c r="G17" s="25">
         <v>0</v>
       </c>
-      <c r="H17" s="30">
+      <c r="H17" s="25">
         <v>0</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
-        <v>372</v>
+        <v>387</v>
       </c>
       <c r="B19" s="19"/>
       <c r="C19" s="19"/>
@@ -6683,84 +6793,84 @@
         <v>7</v>
       </c>
       <c r="D20" s="57" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E20" s="57" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F20" s="57" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G20" s="57" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="H20" s="57" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>373</v>
-      </c>
-      <c r="D21" s="29">
+        <v>388</v>
+      </c>
+      <c r="D21" s="26">
         <v>0.13663808664259913</v>
       </c>
-      <c r="E21" s="29">
+      <c r="E21" s="26">
         <v>0.4067620818062212</v>
       </c>
-      <c r="F21" s="29">
+      <c r="F21" s="26">
         <v>0.5058728257176494</v>
       </c>
-      <c r="G21" s="29">
+      <c r="G21" s="26">
         <v>0.5596038436877832</v>
       </c>
-      <c r="H21" s="29">
+      <c r="H21" s="26">
         <v>0.5600748662293807</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>334</v>
+        <v>348</v>
       </c>
       <c r="D22" s="56" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
       <c r="E22" s="56" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
       <c r="F22" s="56" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
       <c r="G22" s="56" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
       <c r="H22" s="56" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="D23" s="29">
+        <v>214</v>
+      </c>
+      <c r="D23" s="26">
         <v>0.48</v>
       </c>
-      <c r="E23" s="29">
+      <c r="E23" s="26">
         <v>0.72</v>
       </c>
-      <c r="F23" s="29">
+      <c r="F23" s="26">
         <v>0.88</v>
       </c>
-      <c r="G23" s="29">
+      <c r="G23" s="26">
         <v>1</v>
       </c>
-      <c r="H23" s="29">
+      <c r="H23" s="26">
         <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
-        <v>374</v>
+        <v>389</v>
       </c>
       <c r="D24" s="50">
         <v>12</v>
@@ -6778,22 +6888,180 @@
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="14" t="s">
-        <v>375</v>
-      </c>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
+    <row r="26" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="19" t="s">
+        <v>390</v>
+      </c>
+      <c r="B26" s="19"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="19"/>
+      <c r="H26" s="19"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>7</v>
+      </c>
+      <c r="B27" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" t="s">
+        <v>7</v>
+      </c>
+      <c r="D27" s="57" t="s">
+        <v>106</v>
+      </c>
+      <c r="E27" s="57" t="s">
+        <v>107</v>
+      </c>
+      <c r="F27" s="57" t="s">
+        <v>108</v>
+      </c>
+      <c r="G27" s="57" t="s">
+        <v>109</v>
+      </c>
+      <c r="H27" s="57" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="11" t="s">
+        <v>391</v>
+      </c>
+      <c r="D28" s="50">
+        <v>11</v>
+      </c>
+      <c r="E28" s="50">
+        <v>11</v>
+      </c>
+      <c r="F28" s="50">
+        <v>11</v>
+      </c>
+      <c r="G28" s="50">
+        <v>11</v>
+      </c>
+      <c r="H28" s="50">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="11" t="s">
+        <v>392</v>
+      </c>
+      <c r="D29" s="26">
+        <v>0.44</v>
+      </c>
+      <c r="E29" s="26">
+        <v>0.44</v>
+      </c>
+      <c r="F29" s="26">
+        <v>0.44</v>
+      </c>
+      <c r="G29" s="26">
+        <v>0.44</v>
+      </c>
+      <c r="H29" s="26">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="11" t="s">
+        <v>393</v>
+      </c>
+      <c r="D30" s="56">
+        <v>1.56</v>
+      </c>
+      <c r="E30" s="56">
+        <v>14.81</v>
+      </c>
+      <c r="F30" s="56">
+        <v>25.89</v>
+      </c>
+      <c r="G30" s="56">
+        <v>34.9</v>
+      </c>
+      <c r="H30" s="56">
+        <v>36.05</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" s="11" t="s">
+        <v>394</v>
+      </c>
+      <c r="D31" s="25">
+        <v>18898</v>
+      </c>
+      <c r="E31" s="25">
+        <v>115034</v>
+      </c>
+      <c r="F31" s="25">
+        <v>288247</v>
+      </c>
+      <c r="G31" s="25">
+        <v>524160</v>
+      </c>
+      <c r="H31" s="25">
+        <v>768075</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="11" t="s">
+        <v>395</v>
+      </c>
+      <c r="D32" s="56" t="s">
+        <v>349</v>
+      </c>
+      <c r="E32" s="56">
+        <v>9.71</v>
+      </c>
+      <c r="F32" s="56">
+        <v>20.63</v>
+      </c>
+      <c r="G32" s="56">
+        <v>26.78</v>
+      </c>
+      <c r="H32" s="56">
+        <v>27.68</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" s="11" t="s">
+        <v>396</v>
+      </c>
+      <c r="D33" s="25">
+        <v>4523</v>
+      </c>
+      <c r="E33" s="25">
+        <v>65131</v>
+      </c>
+      <c r="F33" s="25">
+        <v>201757</v>
+      </c>
+      <c r="G33" s="25">
+        <v>381152</v>
+      </c>
+      <c r="H33" s="25">
+        <v>566866</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" s="14" t="s">
+        <v>397</v>
+      </c>
+      <c r="B35" s="14"/>
+      <c r="C35" s="14"/>
+      <c r="D35" s="14"/>
+      <c r="E35" s="14"/>
+      <c r="F35" s="14"/>
+      <c r="G35" s="14"/>
+      <c r="H35" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A26:H26"/>
+    <mergeCell ref="A35:H35"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -6821,7 +7089,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>376</v>
+        <v>398</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -6833,7 +7101,7 @@
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B3" s="58" t="s">
-        <v>377</v>
+        <v>399</v>
       </c>
       <c r="C3" s="58"/>
       <c r="D3" s="58"/>
@@ -6845,41 +7113,41 @@
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B4" s="59" t="s">
-        <v>378</v>
+        <v>400</v>
       </c>
       <c r="D4" s="60" t="s">
-        <v>379</v>
+        <v>401</v>
       </c>
       <c r="F4" s="61" t="s">
-        <v>380</v>
+        <v>402</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" s="19" t="s">
-        <v>381</v>
+        <v>403</v>
       </c>
       <c r="C6" s="62" t="s">
-        <v>382</v>
+        <v>404</v>
       </c>
       <c r="D6" s="62" t="s">
-        <v>383</v>
+        <v>405</v>
       </c>
       <c r="E6" s="62" t="s">
-        <v>384</v>
+        <v>406</v>
       </c>
       <c r="F6" s="62" t="s">
-        <v>385</v>
+        <v>407</v>
       </c>
       <c r="G6" s="62" t="s">
-        <v>386</v>
+        <v>408</v>
       </c>
       <c r="H6" s="62" t="s">
-        <v>387</v>
+        <v>409</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="11" t="s">
-        <v>374</v>
+        <v>389</v>
       </c>
       <c r="C7" s="63">
         <v>12</v>
@@ -6899,7 +7167,7 @@
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="11" t="s">
-        <v>330</v>
+        <v>344</v>
       </c>
       <c r="C8" s="64">
         <v>184666.66666666666</v>
@@ -6919,7 +7187,7 @@
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="11" t="s">
-        <v>292</v>
+        <v>305</v>
       </c>
       <c r="C9" s="64">
         <v>118934.16666666667</v>
@@ -6939,7 +7207,7 @@
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="11" t="s">
-        <v>293</v>
+        <v>306</v>
       </c>
       <c r="C10" s="64">
         <v>40500</v>
@@ -6959,7 +7227,7 @@
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="11" t="s">
-        <v>294</v>
+        <v>307</v>
       </c>
       <c r="C11" s="64">
         <v>0</v>
@@ -6979,7 +7247,7 @@
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="10" t="s">
-        <v>273</v>
+        <v>286</v>
       </c>
       <c r="C12" s="65">
         <v>25232.49999999997</v>
@@ -6999,7 +7267,7 @@
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="10" t="s">
-        <v>337</v>
+        <v>351</v>
       </c>
       <c r="C13" s="65">
         <v>62170</v>
@@ -7019,7 +7287,7 @@
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="10" t="s">
-        <v>373</v>
+        <v>388</v>
       </c>
       <c r="C14" s="66">
         <v>0.13663808664259913</v>
@@ -7039,7 +7307,7 @@
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="10" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="C15" s="67">
         <v>15388.888888888889</v>
@@ -7057,12 +7325,12 @@
         <v>20643.4</v>
       </c>
       <c r="H15" s="68" t="s">
-        <v>388</v>
+        <v>410</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="10" t="s">
-        <v>276</v>
+        <v>289</v>
       </c>
       <c r="C16" s="69">
         <v>13286.180555555557</v>
@@ -7082,7 +7350,7 @@
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="11" t="s">
-        <v>389</v>
+        <v>411</v>
       </c>
       <c r="C17" s="64">
         <v>500</v>
@@ -7102,7 +7370,7 @@
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="11" t="s">
-        <v>390</v>
+        <v>412</v>
       </c>
       <c r="C18" s="70">
         <v>3000</v>
@@ -7120,12 +7388,12 @@
         <v>1620.7326864000001</v>
       </c>
       <c r="H18" s="68" t="s">
-        <v>391</v>
+        <v>413</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="10" t="s">
-        <v>392</v>
+        <v>414</v>
       </c>
       <c r="C19" s="71">
         <v>2102.7083333333308</v>
@@ -7145,7 +7413,7 @@
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="10" t="s">
-        <v>393</v>
+        <v>415</v>
       </c>
       <c r="C20" s="72">
         <v>0.6440478339350181</v>
@@ -7163,12 +7431,12 @@
         <v>0.3112544307081392</v>
       </c>
       <c r="H20" s="68" t="s">
-        <v>394</v>
+        <v>416</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="10" t="s">
-        <v>395</v>
+        <v>417</v>
       </c>
       <c r="C21" s="72">
         <v>0.19494584837545129</v>
@@ -7186,12 +7454,12 @@
         <v>0.07851093746185223</v>
       </c>
       <c r="H21" s="68" t="s">
-        <v>396</v>
+        <v>418</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="10" t="s">
-        <v>397</v>
+        <v>419</v>
       </c>
       <c r="C22" s="66">
         <v>0.13663808664259922</v>
@@ -7209,12 +7477,12 @@
         <v>0.5600748662293809</v>
       </c>
       <c r="H22" s="68" t="s">
-        <v>398</v>
+        <v>420</v>
       </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B23" s="10" t="s">
-        <v>399</v>
+        <v>421</v>
       </c>
       <c r="C23" s="73">
         <v>3</v>
@@ -7232,63 +7500,63 @@
         <v>3</v>
       </c>
       <c r="H23" s="68" t="s">
-        <v>400</v>
+        <v>422</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" s="10" t="s">
-        <v>334</v>
+        <v>348</v>
       </c>
       <c r="C24" s="74" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
       <c r="D24" s="74" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
       <c r="E24" s="74" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
       <c r="F24" s="74" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
       <c r="G24" s="74" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
       <c r="H24" s="68" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B25" s="10" t="s">
-        <v>401</v>
+        <v>423</v>
       </c>
       <c r="C25" s="42" t="str">
-        <f>IF('5-Year Operating Stmt'!B17&gt;=0,"✓ Break-even","")</f>
+        <f>IF('5-Year Operating Stmt'!B18&gt;=0,"✓ Break-even","")</f>
         <v>✓ Break-even</v>
       </c>
       <c r="D25" s="75" t="str">
-        <f>IF(AND('5-Year Operating Stmt'!C17&gt;=0,'5-Year Operating Stmt'!B17&lt;0),"✓ Break-even","")</f>
+        <f>IF(AND('5-Year Operating Stmt'!C18&gt;=0,'5-Year Operating Stmt'!B18&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
       <c r="E25" s="75" t="str">
-        <f>IF(AND('5-Year Operating Stmt'!D17&gt;=0,'5-Year Operating Stmt'!C17&lt;0),"✓ Break-even","")</f>
+        <f>IF(AND('5-Year Operating Stmt'!D18&gt;=0,'5-Year Operating Stmt'!C18&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
       <c r="F25" s="75" t="str">
-        <f>IF(AND('5-Year Operating Stmt'!E17&gt;=0,'5-Year Operating Stmt'!D17&lt;0),"✓ Break-even","")</f>
+        <f>IF(AND('5-Year Operating Stmt'!E18&gt;=0,'5-Year Operating Stmt'!D18&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
       <c r="G25" s="75" t="str">
-        <f>IF(AND('5-Year Operating Stmt'!F17&gt;=0,'5-Year Operating Stmt'!E17&lt;0),"✓ Break-even","")</f>
+        <f>IF(AND('5-Year Operating Stmt'!F18&gt;=0,'5-Year Operating Stmt'!E18&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
       <c r="H25" s="68" t="s">
-        <v>382</v>
+        <v>404</v>
       </c>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="10" t="s">
-        <v>402</v>
+        <v>424</v>
       </c>
       <c r="C26" s="76">
         <v>5</v>
@@ -7306,12 +7574,12 @@
         <v>52</v>
       </c>
       <c r="H26" s="68" t="s">
-        <v>403</v>
+        <v>425</v>
       </c>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27" s="10" t="s">
-        <v>338</v>
+        <v>353</v>
       </c>
       <c r="C27" s="73">
         <v>142</v>
@@ -7329,22 +7597,22 @@
         <v>1586</v>
       </c>
       <c r="H27" s="68" t="s">
-        <v>404</v>
+        <v>426</v>
       </c>
     </row>
     <row r="29" ht="24" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B29" s="19" t="s">
-        <v>405</v>
+        <v>427</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>406</v>
+        <v>428</v>
       </c>
       <c r="D29" s="19" t="s">
-        <v>407</v>
+        <v>429</v>
       </c>
       <c r="E29" s="19"/>
       <c r="F29" s="19" t="s">
-        <v>408</v>
+        <v>430</v>
       </c>
       <c r="G29" s="19"/>
       <c r="H29" s="19"/>
@@ -7352,17 +7620,17 @@
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B30" s="44" t="s">
-        <v>409</v>
+        <v>431</v>
       </c>
       <c r="C30" s="42" t="s">
-        <v>410</v>
+        <v>432</v>
       </c>
       <c r="D30" s="78" t="s">
-        <v>411</v>
+        <v>433</v>
       </c>
       <c r="E30" s="78"/>
       <c r="F30" s="79" t="s">
-        <v>412</v>
+        <v>434</v>
       </c>
       <c r="G30" s="79"/>
       <c r="H30" s="79"/>
@@ -7370,17 +7638,17 @@
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B31" s="44" t="s">
-        <v>413</v>
+        <v>435</v>
       </c>
       <c r="C31" s="42" t="s">
-        <v>410</v>
+        <v>432</v>
       </c>
       <c r="D31" s="78" t="s">
-        <v>414</v>
+        <v>436</v>
       </c>
       <c r="E31" s="78"/>
       <c r="F31" s="79" t="s">
-        <v>415</v>
+        <v>437</v>
       </c>
       <c r="G31" s="79"/>
       <c r="H31" s="79"/>
@@ -7388,17 +7656,17 @@
     </row>
     <row r="32" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B32" s="44" t="s">
-        <v>416</v>
+        <v>438</v>
       </c>
       <c r="C32" s="42" t="s">
-        <v>410</v>
+        <v>432</v>
       </c>
       <c r="D32" s="78" t="s">
-        <v>417</v>
+        <v>439</v>
       </c>
       <c r="E32" s="78"/>
       <c r="F32" s="79" t="s">
-        <v>418</v>
+        <v>440</v>
       </c>
       <c r="G32" s="79"/>
       <c r="H32" s="79"/>
@@ -7406,17 +7674,17 @@
     </row>
     <row r="33" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B33" s="44" t="s">
-        <v>419</v>
+        <v>441</v>
       </c>
       <c r="C33" s="42" t="s">
-        <v>410</v>
+        <v>432</v>
       </c>
       <c r="D33" s="78" t="s">
-        <v>420</v>
+        <v>442</v>
       </c>
       <c r="E33" s="78"/>
       <c r="F33" s="79" t="s">
-        <v>421</v>
+        <v>443</v>
       </c>
       <c r="G33" s="79"/>
       <c r="H33" s="79"/>
@@ -7424,17 +7692,17 @@
     </row>
     <row r="34" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B34" s="44" t="s">
-        <v>422</v>
+        <v>444</v>
       </c>
       <c r="C34" s="42" t="s">
-        <v>410</v>
+        <v>432</v>
       </c>
       <c r="D34" s="78" t="s">
-        <v>423</v>
+        <v>445</v>
       </c>
       <c r="E34" s="78"/>
       <c r="F34" s="79" t="s">
-        <v>424</v>
+        <v>446</v>
       </c>
       <c r="G34" s="79"/>
       <c r="H34" s="79"/>
@@ -7442,17 +7710,17 @@
     </row>
     <row r="35" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B35" s="44" t="s">
-        <v>425</v>
+        <v>447</v>
       </c>
       <c r="C35" s="42" t="s">
-        <v>410</v>
+        <v>432</v>
       </c>
       <c r="D35" s="78" t="s">
-        <v>426</v>
+        <v>448</v>
       </c>
       <c r="E35" s="78"/>
       <c r="F35" s="79" t="s">
-        <v>427</v>
+        <v>449</v>
       </c>
       <c r="G35" s="79"/>
       <c r="H35" s="79"/>
@@ -7460,10 +7728,10 @@
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B37" s="44" t="s">
-        <v>428</v>
+        <v>450</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>429</v>
+        <v>451</v>
       </c>
       <c r="D37" s="10"/>
       <c r="E37" s="10"/>
@@ -7471,7 +7739,7 @@
     </row>
     <row r="39" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B39" s="80" t="s">
-        <v>430</v>
+        <v>452</v>
       </c>
       <c r="C39" s="80"/>
       <c r="D39" s="80"/>
@@ -7607,109 +7875,109 @@
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>431</v>
+        <v>453</v>
       </c>
       <c r="B3" s="19"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="81" t="s">
-        <v>432</v>
+        <v>454</v>
       </c>
       <c r="B4" s="81"/>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="19" t="s">
-        <v>433</v>
+        <v>455</v>
       </c>
       <c r="B6" s="19"/>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="81" t="s">
-        <v>432</v>
+        <v>454</v>
       </c>
       <c r="B7" s="81"/>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
-        <v>434</v>
+        <v>456</v>
       </c>
       <c r="B9" s="19"/>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="81" t="s">
-        <v>432</v>
+        <v>454</v>
       </c>
       <c r="B10" s="81"/>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
-        <v>435</v>
+        <v>457</v>
       </c>
       <c r="B12" s="19"/>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="81" t="s">
-        <v>432</v>
+        <v>454</v>
       </c>
       <c r="B13" s="81"/>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
-        <v>436</v>
+        <v>458</v>
       </c>
       <c r="B15" s="19"/>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="81" t="s">
-        <v>432</v>
+        <v>454</v>
       </c>
       <c r="B16" s="81"/>
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="19" t="s">
-        <v>437</v>
+        <v>459</v>
       </c>
       <c r="B18" s="19"/>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="81" t="s">
-        <v>432</v>
+        <v>454</v>
       </c>
       <c r="B19" s="81"/>
     </row>
     <row r="21" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="19" t="s">
-        <v>438</v>
+        <v>460</v>
       </c>
       <c r="B21" s="19"/>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="81" t="s">
-        <v>432</v>
+        <v>454</v>
       </c>
       <c r="B22" s="81"/>
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="19" t="s">
-        <v>439</v>
+        <v>461</v>
       </c>
       <c r="B24" s="19"/>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="81" t="s">
-        <v>432</v>
+        <v>454</v>
       </c>
       <c r="B25" s="81"/>
     </row>
     <row r="27" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="19" t="s">
-        <v>440</v>
+        <v>462</v>
       </c>
       <c r="B27" s="19"/>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="81" t="s">
-        <v>432</v>
+        <v>454</v>
       </c>
       <c r="B28" s="81"/>
     </row>
@@ -7739,6 +8007,52 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="32" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="50" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="81" t="s">
+        <v>463</v>
+      </c>
+      <c r="B3" s="81"/>
+      <c r="C3" s="81"/>
+      <c r="D3" s="81"/>
+      <c r="E3" s="81"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A3:E3"/>
+  </mergeCells>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddFooter>&amp;L&amp;8SchoolStack Budget&amp;C&amp;8Confidential&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
@@ -7749,21 +8063,21 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
-        <v>441</v>
+        <v>464</v>
       </c>
       <c r="B1" s="21"/>
       <c r="C1" s="21"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="82" t="s">
-        <v>442</v>
+        <v>465</v>
       </c>
       <c r="B2" s="82"/>
       <c r="C2" s="82"/>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="83" t="s">
-        <v>443</v>
+        <v>466</v>
       </c>
       <c r="B4" s="83"/>
       <c r="C4" s="83"/>
@@ -7782,7 +8096,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF328555"/>
@@ -7803,7 +8117,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B1" s="15" t="s">
-        <v>444</v>
+        <v>467</v>
       </c>
       <c r="C1" s="15"/>
       <c r="D1" s="15"/>
@@ -7814,7 +8128,7 @@
     </row>
     <row r="2" ht="44" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="84" t="s">
-        <v>445</v>
+        <v>468</v>
       </c>
       <c r="C2" s="84"/>
       <c r="D2" s="84"/>
@@ -7825,150 +8139,150 @@
     </row>
     <row r="4" ht="28" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B4" s="85" t="s">
-        <v>446</v>
+        <v>469</v>
       </c>
       <c r="C4" s="85" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="D4" s="85" t="s">
-        <v>447</v>
+        <v>470</v>
       </c>
       <c r="E4" s="85" t="s">
-        <v>448</v>
+        <v>471</v>
       </c>
       <c r="F4" s="85" t="s">
-        <v>449</v>
+        <v>472</v>
       </c>
       <c r="G4" s="85" t="s">
-        <v>450</v>
+        <v>473</v>
       </c>
       <c r="H4" s="85" t="s">
-        <v>451</v>
+        <v>474</v>
       </c>
     </row>
     <row r="5" ht="64" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="86"/>
       <c r="B5" s="87" t="s">
-        <v>452</v>
+        <v>475</v>
       </c>
       <c r="C5" s="88" t="s">
-        <v>453</v>
+        <v>476</v>
       </c>
       <c r="D5" s="89" t="s">
-        <v>454</v>
+        <v>477</v>
       </c>
       <c r="E5" s="88" t="s">
-        <v>455</v>
+        <v>478</v>
       </c>
       <c r="F5" s="90" t="s">
-        <v>456</v>
+        <v>479</v>
       </c>
       <c r="G5" s="88" t="s">
-        <v>457</v>
+        <v>480</v>
       </c>
       <c r="H5" s="88" t="s">
-        <v>458</v>
+        <v>481</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="86"/>
       <c r="B6" s="87" t="s">
-        <v>459</v>
+        <v>482</v>
       </c>
       <c r="C6" s="88" t="s">
-        <v>460</v>
+        <v>483</v>
       </c>
       <c r="D6" s="89" t="s">
-        <v>454</v>
+        <v>477</v>
       </c>
       <c r="E6" s="88" t="s">
-        <v>461</v>
+        <v>484</v>
       </c>
       <c r="F6" s="90" t="s">
-        <v>462</v>
+        <v>485</v>
       </c>
       <c r="G6" s="88" t="s">
-        <v>463</v>
+        <v>486</v>
       </c>
       <c r="H6" s="88" t="s">
-        <v>464</v>
+        <v>487</v>
       </c>
     </row>
     <row r="7" ht="64" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="91"/>
       <c r="B7" s="87" t="s">
-        <v>465</v>
+        <v>488</v>
       </c>
       <c r="C7" s="88" t="s">
-        <v>466</v>
+        <v>489</v>
       </c>
       <c r="D7" s="92" t="s">
-        <v>467</v>
+        <v>490</v>
       </c>
       <c r="E7" s="88" t="s">
-        <v>468</v>
+        <v>491</v>
       </c>
       <c r="F7" s="90" t="s">
-        <v>469</v>
+        <v>492</v>
       </c>
       <c r="G7" s="88" t="s">
-        <v>470</v>
+        <v>493</v>
       </c>
       <c r="H7" s="88" t="s">
-        <v>471</v>
+        <v>494</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="93"/>
       <c r="B8" s="87" t="s">
-        <v>472</v>
+        <v>495</v>
       </c>
       <c r="C8" s="88" t="s">
-        <v>460</v>
+        <v>483</v>
       </c>
       <c r="D8" s="94" t="s">
-        <v>473</v>
+        <v>496</v>
       </c>
       <c r="E8" s="88" t="s">
-        <v>468</v>
+        <v>491</v>
       </c>
       <c r="F8" s="90" t="s">
-        <v>474</v>
+        <v>497</v>
       </c>
       <c r="G8" s="88" t="s">
-        <v>475</v>
+        <v>498</v>
       </c>
       <c r="H8" s="88" t="s">
-        <v>476</v>
+        <v>499</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="93"/>
       <c r="B9" s="87" t="s">
-        <v>477</v>
+        <v>500</v>
       </c>
       <c r="C9" s="88" t="s">
-        <v>466</v>
+        <v>489</v>
       </c>
       <c r="D9" s="94" t="s">
-        <v>473</v>
+        <v>496</v>
       </c>
       <c r="E9" s="88" t="s">
-        <v>468</v>
+        <v>491</v>
       </c>
       <c r="F9" s="90" t="s">
-        <v>478</v>
+        <v>501</v>
       </c>
       <c r="G9" s="88" t="s">
-        <v>479</v>
+        <v>502</v>
       </c>
       <c r="H9" s="88" t="s">
-        <v>480</v>
+        <v>503</v>
       </c>
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B11" s="58" t="s">
-        <v>481</v>
+        <v>504</v>
       </c>
       <c r="C11" s="58"/>
       <c r="D11" s="58"/>
@@ -7996,7 +8310,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G63"/>
+  <dimension ref="A1:G75"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
@@ -8006,7 +8320,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -8020,18 +8334,18 @@
         <v>7</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D2" s="18" t="s">
         <v>7</v>
       </c>
       <c r="E2" s="17" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -8074,10 +8388,10 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -8098,7 +8412,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B12" s="20">
         <v>7</v>
@@ -8106,7 +8420,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B13" s="20">
         <v>25</v>
@@ -8114,7 +8428,7 @@
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B15" s="19"/>
       <c r="C15" s="19"/>
@@ -8127,24 +8441,24 @@
         <v>7</v>
       </c>
       <c r="B16" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E16" s="21" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F16" s="21" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B17" s="22">
         <v>12</v>
@@ -8164,7 +8478,7 @@
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B19" s="19"/>
       <c r="C19" s="19"/>
@@ -8175,33 +8489,33 @@
     </row>
     <row r="20" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="21" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B20" s="21" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C20" s="21" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D20" s="21" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E20" s="21" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F20" s="21" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D21" s="23">
         <v>12000</v>
@@ -8210,18 +8524,18 @@
         <v>0</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="C22" s="11" t="s">
         <v>121</v>
-      </c>
-      <c r="B22" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="C22" s="11" t="s">
-        <v>119</v>
       </c>
       <c r="D22" s="23">
         <v>250</v>
@@ -8230,18 +8544,18 @@
         <v>0</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D23" s="23">
         <v>7000</v>
@@ -8250,18 +8564,18 @@
         <v>0</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D24" s="23">
         <v>5000</v>
@@ -8270,18 +8584,18 @@
         <v>0</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D25" s="23">
         <v>10</v>
@@ -8290,408 +8604,527 @@
         <v>0</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="27" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="27" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="19" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B27" s="19"/>
       <c r="C27" s="19"/>
       <c r="D27" s="19"/>
       <c r="E27" s="19"/>
       <c r="F27" s="19"/>
-      <c r="G27" s="19"/>
-    </row>
-    <row r="28" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="21" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B28" s="21" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>132</v>
+        <v>107</v>
       </c>
       <c r="D28" s="21" t="s">
-        <v>133</v>
+        <v>108</v>
       </c>
       <c r="E28" s="21" t="s">
+        <v>109</v>
+      </c>
+      <c r="F28" s="21" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="F28" s="21" t="s">
+      <c r="B29" s="25">
+        <v>-12000</v>
+      </c>
+      <c r="C29" s="25">
+        <v>-22248</v>
+      </c>
+      <c r="D29" s="25">
+        <v>-28007.76</v>
+      </c>
+      <c r="E29" s="25">
+        <v>-32781.81</v>
+      </c>
+      <c r="F29" s="25">
+        <v>-33765.2643</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="G28" s="21" t="s">
+      <c r="B30" s="25">
+        <v>122500</v>
+      </c>
+      <c r="C30" s="25">
+        <v>227115</v>
+      </c>
+      <c r="D30" s="25">
+        <v>285912.55</v>
+      </c>
+      <c r="E30" s="25">
+        <v>334647.64375</v>
+      </c>
+      <c r="F30" s="25">
+        <v>344687.07306250004</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="11" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="11" t="s">
+      <c r="B31" s="25">
+        <v>4166.666666666667</v>
+      </c>
+      <c r="C31" s="25">
+        <v>5150</v>
+      </c>
+      <c r="D31" s="25">
+        <v>5304.5</v>
+      </c>
+      <c r="E31" s="25">
+        <v>5463.635</v>
+      </c>
+      <c r="F31" s="25">
+        <v>5627.54405</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="B29" s="11" t="s">
+      <c r="B32" s="25">
+        <v>70000</v>
+      </c>
+      <c r="C32" s="25">
+        <v>129780</v>
+      </c>
+      <c r="D32" s="25">
+        <v>163378.59999999998</v>
+      </c>
+      <c r="E32" s="25">
+        <v>191227.225</v>
+      </c>
+      <c r="F32" s="25">
+        <v>196964.04175000003</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="C29" s="11" t="s">
+      <c r="B33" s="26">
+        <v>-0.06498194945848376</v>
+      </c>
+      <c r="C33" s="26">
+        <v>-0.06547438617762959</v>
+      </c>
+      <c r="D33" s="26">
+        <v>-0.06565530962447153</v>
+      </c>
+      <c r="E33" s="26">
+        <v>-0.06575342465753424</v>
+      </c>
+      <c r="F33" s="26">
+        <v>-0.06575342465753424</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="11" t="s">
         <v>139</v>
       </c>
-      <c r="D29" s="25">
+      <c r="B34" s="26">
+        <v>0.6633574007220217</v>
+      </c>
+      <c r="C34" s="26">
+        <v>0.6683843588966354</v>
+      </c>
+      <c r="D34" s="26">
+        <v>0.6702312857498135</v>
+      </c>
+      <c r="E34" s="26">
+        <v>0.6712328767123287</v>
+      </c>
+      <c r="F34" s="26">
+        <v>0.6712328767123287</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="B35" s="26">
+        <v>0.02256317689530686</v>
+      </c>
+      <c r="C35" s="26">
+        <v>0.01515610791148833</v>
+      </c>
+      <c r="D35" s="26">
+        <v>0.012434717731907487</v>
+      </c>
+      <c r="E35" s="26">
+        <v>0.010958904109589041</v>
+      </c>
+      <c r="F35" s="26">
+        <v>0.01095890410958904</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="B36" s="26">
+        <v>0.37906137184115524</v>
+      </c>
+      <c r="C36" s="26">
+        <v>0.38193391936950594</v>
+      </c>
+      <c r="D36" s="26">
+        <v>0.38298930614275056</v>
+      </c>
+      <c r="E36" s="26">
+        <v>0.3835616438356164</v>
+      </c>
+      <c r="F36" s="26">
+        <v>0.3835616438356164</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="B37" s="27">
+        <v>-0.07745225122498264</v>
+      </c>
+      <c r="C37" s="27">
+        <v>-0.1215720233091732</v>
+      </c>
+      <c r="D37" s="27">
+        <v>-0.14944429416974292</v>
+      </c>
+      <c r="E37" s="27">
+        <v>-0.17077853976927615</v>
+      </c>
+      <c r="F37" s="27">
+        <v>-0.1717165314906201</v>
+      </c>
+    </row>
+    <row r="39" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="19" t="s">
+        <v>143</v>
+      </c>
+      <c r="B39" s="19"/>
+      <c r="C39" s="19"/>
+      <c r="D39" s="19"/>
+      <c r="E39" s="19"/>
+      <c r="F39" s="19"/>
+      <c r="G39" s="19"/>
+    </row>
+    <row r="40" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="21" t="s">
+        <v>144</v>
+      </c>
+      <c r="B40" s="21" t="s">
+        <v>114</v>
+      </c>
+      <c r="C40" s="21" t="s">
+        <v>145</v>
+      </c>
+      <c r="D40" s="21" t="s">
+        <v>146</v>
+      </c>
+      <c r="E40" s="21" t="s">
+        <v>147</v>
+      </c>
+      <c r="F40" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="G40" s="21" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="B41" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="C41" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="D41" s="28">
         <v>1</v>
       </c>
-      <c r="E29" s="23">
+      <c r="E41" s="23">
         <v>55000</v>
       </c>
-      <c r="F29" s="24">
+      <c r="F41" s="24">
         <v>0.2</v>
       </c>
-      <c r="G29" s="24">
+      <c r="G41" s="24">
         <v>0.0765</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="B30" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="C30" s="11" t="s">
-        <v>139</v>
-      </c>
-      <c r="D30" s="25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="B42" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="C42" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="D42" s="28">
         <v>1</v>
       </c>
-      <c r="E30" s="23">
+      <c r="E42" s="23">
         <v>45000</v>
       </c>
-      <c r="F30" s="24">
+      <c r="F42" s="24">
         <v>0.2</v>
       </c>
-      <c r="G30" s="24">
+      <c r="G42" s="24">
         <v>0.0765</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="B31" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="C31" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="D31" s="25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="B43" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="C43" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="D43" s="28">
         <v>0.5</v>
       </c>
-      <c r="E31" s="23">
+      <c r="E43" s="23">
         <v>28000</v>
       </c>
-      <c r="F31" s="24">
+      <c r="F43" s="24">
         <v>0</v>
       </c>
-      <c r="G31" s="24">
+      <c r="G43" s="24">
         <v>0.0765</v>
       </c>
     </row>
-    <row r="33" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="B33" s="19"/>
-      <c r="C33" s="19"/>
-      <c r="D33" s="19"/>
-      <c r="E33" s="19"/>
-      <c r="F33" s="19"/>
-      <c r="G33" s="19"/>
-    </row>
-    <row r="34" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="21" t="s">
-        <v>111</v>
-      </c>
-      <c r="B34" s="21" t="s">
-        <v>112</v>
-      </c>
-      <c r="C34" s="21" t="s">
+    <row r="45" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="B45" s="19"/>
+      <c r="C45" s="19"/>
+      <c r="D45" s="19"/>
+      <c r="E45" s="19"/>
+      <c r="F45" s="19"/>
+      <c r="G45" s="19"/>
+    </row>
+    <row r="46" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="21" t="s">
         <v>113</v>
       </c>
-      <c r="D34" s="21" t="s">
+      <c r="B46" s="21" t="s">
         <v>114</v>
       </c>
-      <c r="E34" s="21" t="s">
+      <c r="C46" s="21" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="11" t="s">
+      <c r="D46" s="21" t="s">
+        <v>116</v>
+      </c>
+      <c r="E46" s="21" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="B47" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="C47" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="D47" s="23">
+        <v>2500</v>
+      </c>
+      <c r="E47" s="24">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="B48" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="C48" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="D48" s="23">
+        <v>300</v>
+      </c>
+      <c r="E48" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="B49" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="C49" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="D49" s="23">
+        <v>2400</v>
+      </c>
+      <c r="E49" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="B50" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="C50" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="D50" s="23">
+        <v>500</v>
+      </c>
+      <c r="E50" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="B51" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="C51" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="D51" s="23">
+        <v>300</v>
+      </c>
+      <c r="E51" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="B52" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="C52" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="D52" s="23">
+        <v>3000</v>
+      </c>
+      <c r="E52" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A54" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="B54" s="19"/>
+      <c r="C54" s="19"/>
+      <c r="D54" s="19"/>
+      <c r="E54" s="19"/>
+      <c r="F54" s="19"/>
+      <c r="G54" s="19"/>
+    </row>
+    <row r="55" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="21" t="s">
+        <v>169</v>
+      </c>
+      <c r="B55" s="21" t="s">
         <v>145</v>
       </c>
-      <c r="B35" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="C35" s="11" t="s">
+      <c r="C55" s="21" t="s">
+        <v>170</v>
+      </c>
+      <c r="D55" s="21" t="s">
         <v>147</v>
       </c>
-      <c r="D35" s="23">
-        <v>2500</v>
-      </c>
-      <c r="E35" s="24">
+      <c r="E55" s="21" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="B56" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="C56" s="23">
+        <v>30000</v>
+      </c>
+      <c r="D56" s="24">
+        <v>0.06</v>
+      </c>
+      <c r="E56" s="22">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A58" s="19" t="s">
+        <v>174</v>
+      </c>
+      <c r="B58" s="19"/>
+      <c r="C58" s="19"/>
+      <c r="D58" s="19"/>
+      <c r="E58" s="19"/>
+      <c r="F58" s="19"/>
+      <c r="G58" s="19"/>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="B59" s="24">
         <v>0.03</v>
       </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="11" t="s">
-        <v>148</v>
-      </c>
-      <c r="B36" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="C36" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="D36" s="23">
-        <v>300</v>
-      </c>
-      <c r="E36" s="24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="11" t="s">
-        <v>149</v>
-      </c>
-      <c r="B37" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="C37" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="D37" s="23">
-        <v>2400</v>
-      </c>
-      <c r="E37" s="24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="B38" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="C38" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="D38" s="23">
-        <v>500</v>
-      </c>
-      <c r="E38" s="24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="11" t="s">
-        <v>152</v>
-      </c>
-      <c r="B39" s="11" t="s">
-        <v>152</v>
-      </c>
-      <c r="C39" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="D39" s="23">
-        <v>300</v>
-      </c>
-      <c r="E39" s="24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="11" t="s">
-        <v>153</v>
-      </c>
-      <c r="B40" s="11" t="s">
-        <v>154</v>
-      </c>
-      <c r="C40" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="D40" s="23">
-        <v>3000</v>
-      </c>
-      <c r="E40" s="24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="19" t="s">
-        <v>155</v>
-      </c>
-      <c r="B42" s="19"/>
-      <c r="C42" s="19"/>
-      <c r="D42" s="19"/>
-      <c r="E42" s="19"/>
-      <c r="F42" s="19"/>
-      <c r="G42" s="19"/>
-    </row>
-    <row r="43" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="21" t="s">
-        <v>156</v>
-      </c>
-      <c r="B43" s="21" t="s">
-        <v>132</v>
-      </c>
-      <c r="C43" s="21" t="s">
-        <v>157</v>
-      </c>
-      <c r="D43" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="E43" s="21" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="11" t="s">
-        <v>159</v>
-      </c>
-      <c r="B44" s="11" t="s">
-        <v>160</v>
-      </c>
-      <c r="C44" s="23">
-        <v>30000</v>
-      </c>
-      <c r="D44" s="24">
-        <v>0.06</v>
-      </c>
-      <c r="E44" s="22">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="46" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" s="19" t="s">
-        <v>161</v>
-      </c>
-      <c r="B46" s="19"/>
-      <c r="C46" s="19"/>
-      <c r="D46" s="19"/>
-      <c r="E46" s="19"/>
-      <c r="F46" s="19"/>
-      <c r="G46" s="19"/>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="11" t="s">
-        <v>162</v>
-      </c>
-      <c r="B47" s="24">
-        <v>0.03</v>
-      </c>
-      <c r="C47" s="26" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="11" t="s">
-        <v>164</v>
-      </c>
-      <c r="B48" s="24">
-        <v>0.03</v>
-      </c>
-      <c r="C48" s="26" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="11" t="s">
-        <v>166</v>
-      </c>
-      <c r="B49" s="25">
-        <v>0.8333333333333334</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="11" t="s">
-        <v>167</v>
-      </c>
-      <c r="B50" s="23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" s="11" t="s">
-        <v>168</v>
-      </c>
-      <c r="B51" s="20" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" s="11" t="s">
-        <v>170</v>
-      </c>
-      <c r="B52" s="24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" s="11" t="s">
-        <v>171</v>
-      </c>
-      <c r="B53" s="24">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" s="11" t="s">
-        <v>172</v>
-      </c>
-      <c r="B54" s="24">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="B55" s="24">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56" s="11" t="s">
-        <v>174</v>
-      </c>
-      <c r="B56" s="24">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57" s="11" t="s">
-        <v>175</v>
-      </c>
-      <c r="B57" s="24">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="59" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="19" t="s">
+      <c r="C59" s="29" t="s">
         <v>176</v>
       </c>
-      <c r="B59" s="19"/>
-      <c r="C59" s="19"/>
-      <c r="D59" s="19"/>
-      <c r="E59" s="19"/>
-      <c r="F59" s="19"/>
-      <c r="G59" s="19"/>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="B60" s="20" t="s">
+      <c r="B60" s="24">
+        <v>0.03</v>
+      </c>
+      <c r="C60" s="29" t="s">
         <v>178</v>
       </c>
     </row>
@@ -8699,24 +9132,115 @@
       <c r="A61" s="11" t="s">
         <v>179</v>
       </c>
-      <c r="B61" s="20" t="s">
-        <v>180</v>
+      <c r="B61" s="28">
+        <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="B62" s="24">
-        <v>1</v>
+        <v>180</v>
+      </c>
+      <c r="B62" s="23">
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="B63" s="20" t="s">
         <v>182</v>
       </c>
-      <c r="B63" s="20" t="s">
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" s="11" t="s">
         <v>183</v>
+      </c>
+      <c r="B64" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="B65" s="24">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="B66" s="24">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="B67" s="24">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="B68" s="24">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="B69" s="24">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="71" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A71" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="B71" s="19"/>
+      <c r="C71" s="19"/>
+      <c r="D71" s="19"/>
+      <c r="E71" s="19"/>
+      <c r="F71" s="19"/>
+      <c r="G71" s="19"/>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="B72" s="20" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="B73" s="20" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="B74" s="24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="B75" s="20" t="s">
+        <v>196</v>
       </c>
     </row>
   </sheetData>
@@ -8751,10 +9275,10 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -8775,10 +9299,10 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -8791,7 +9315,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="B8" s="11" t="s">
         <v>46</v>
@@ -8799,66 +9323,66 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>189</v>
+        <v>202</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>191</v>
+        <v>204</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>197</v>
+        <v>210</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
     </row>
   </sheetData>
@@ -8901,24 +9425,24 @@
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="19" t="s">
-        <v>200</v>
+        <v>213</v>
       </c>
       <c r="B5" s="19"/>
       <c r="C5" s="19"/>
@@ -8928,27 +9452,27 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="B6" s="27">
+        <v>111</v>
+      </c>
+      <c r="B6" s="30">
         <v>12</v>
       </c>
-      <c r="C6" s="27">
+      <c r="C6" s="30">
         <v>18</v>
       </c>
-      <c r="D6" s="27">
+      <c r="D6" s="30">
         <v>22</v>
       </c>
-      <c r="E6" s="27">
+      <c r="E6" s="30">
         <v>25</v>
       </c>
-      <c r="F6" s="27">
+      <c r="F6" s="30">
         <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B7" s="22">
         <v>25</v>
@@ -8956,49 +9480,49 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="B8" s="28">
+        <v>214</v>
+      </c>
+      <c r="B8" s="31">
         <f>B6/$B$7</f>
         <v>0.48</v>
       </c>
-      <c r="C8" s="28">
+      <c r="C8" s="31">
         <f>C6/$B$7</f>
         <v>0.72</v>
       </c>
-      <c r="D8" s="28">
+      <c r="D8" s="31">
         <f>D6/$B$7</f>
         <v>0.88</v>
       </c>
-      <c r="E8" s="28">
+      <c r="E8" s="31">
         <f>E6/$B$7</f>
         <v>1</v>
       </c>
-      <c r="F8" s="28">
+      <c r="F8" s="31">
         <f>F6/$B$7</f>
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="C10" s="29">
+        <v>215</v>
+      </c>
+      <c r="C10" s="26">
         <f>IF(B6=0,0,(C6-B6)/B6)</f>
         <v>0.5</v>
       </c>
-      <c r="D10" s="29">
+      <c r="D10" s="26">
         <f>IF(C6=0,0,(D6-C6)/C6)</f>
         <v>0.22222222</v>
       </c>
-      <c r="E10" s="29">
+      <c r="E10" s="26">
         <f>IF(D6=0,0,(E6-D6)/D6)</f>
         <v>0.13636364</v>
       </c>
-      <c r="F10" s="29" t="str">
+      <c r="F10" s="26" t="str">
         <f>IF(E6=0,0,(F6-E6)/E6)</f>
         <v>0</v>
       </c>
@@ -9029,7 +9553,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -9042,24 +9566,24 @@
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -9069,72 +9593,72 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="B5" s="30">
+        <v>119</v>
+      </c>
+      <c r="B5" s="25">
         <v>144000</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="25">
         <v>222480</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="25">
         <v>280078</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="25">
         <v>327818</v>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="25">
         <v>337653</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="B6" s="30">
+        <v>123</v>
+      </c>
+      <c r="B6" s="25">
         <v>3000</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="25">
         <v>4635</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="25">
         <v>5835</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="25">
         <v>6830</v>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="25">
         <v>7034</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>205</v>
-      </c>
-      <c r="B7" s="31">
+        <v>218</v>
+      </c>
+      <c r="B7" s="32">
         <f>SUM(B5,B6)</f>
         <v>147000</v>
       </c>
-      <c r="C7" s="31">
+      <c r="C7" s="32">
         <f>SUM(C5,C6)</f>
         <v>227115</v>
       </c>
-      <c r="D7" s="31">
+      <c r="D7" s="32">
         <f>SUM(D5,D6)</f>
         <v>285913</v>
       </c>
-      <c r="E7" s="31">
+      <c r="E7" s="32">
         <f>SUM(E5,E6)</f>
         <v>334648</v>
       </c>
-      <c r="F7" s="31">
+      <c r="F7" s="32">
         <f>SUM(F5,F6)</f>
         <v>344687</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="19" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="B8" s="19"/>
       <c r="C8" s="19"/>
@@ -9144,52 +9668,52 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>127</v>
-      </c>
-      <c r="B9" s="30">
+        <v>129</v>
+      </c>
+      <c r="B9" s="25">
         <v>-10</v>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="25">
         <v>-10</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="25">
         <v>-11</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="25">
         <v>-11</v>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="25">
         <v>-11</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>207</v>
-      </c>
-      <c r="B10" s="31">
+        <v>220</v>
+      </c>
+      <c r="B10" s="32">
         <f>SUM(B9)</f>
         <v>-10</v>
       </c>
-      <c r="C10" s="31">
+      <c r="C10" s="32">
         <f>SUM(C9)</f>
         <v>-10</v>
       </c>
-      <c r="D10" s="31">
+      <c r="D10" s="32">
         <f>SUM(D9)</f>
         <v>-11</v>
       </c>
-      <c r="E10" s="31">
+      <c r="E10" s="32">
         <f>SUM(E9)</f>
         <v>-11</v>
       </c>
-      <c r="F10" s="31">
+      <c r="F10" s="32">
         <f>SUM(F9)</f>
         <v>-11</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>208</v>
+        <v>221</v>
       </c>
       <c r="B11" s="19"/>
       <c r="C11" s="19"/>
@@ -9199,52 +9723,52 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="B12" s="30">
+        <v>124</v>
+      </c>
+      <c r="B12" s="25">
         <v>84000</v>
       </c>
-      <c r="C12" s="30">
+      <c r="C12" s="25">
         <v>129780</v>
       </c>
-      <c r="D12" s="30">
+      <c r="D12" s="25">
         <v>163379</v>
       </c>
-      <c r="E12" s="30">
+      <c r="E12" s="25">
         <v>191227</v>
       </c>
-      <c r="F12" s="30">
+      <c r="F12" s="25">
         <v>196964</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>209</v>
-      </c>
-      <c r="B13" s="31">
+        <v>222</v>
+      </c>
+      <c r="B13" s="32">
         <f>SUM(B12)</f>
         <v>84000</v>
       </c>
-      <c r="C13" s="31">
+      <c r="C13" s="32">
         <f>SUM(C12)</f>
         <v>129780</v>
       </c>
-      <c r="D13" s="31">
+      <c r="D13" s="32">
         <f>SUM(D12)</f>
         <v>163379</v>
       </c>
-      <c r="E13" s="31">
+      <c r="E13" s="32">
         <f>SUM(E12)</f>
         <v>191227</v>
       </c>
-      <c r="F13" s="31">
+      <c r="F13" s="32">
         <f>SUM(F12)</f>
         <v>196964</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="19" t="s">
-        <v>210</v>
+        <v>223</v>
       </c>
       <c r="B14" s="19"/>
       <c r="C14" s="19"/>
@@ -9254,70 +9778,70 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B15" s="23">
         <v>5000</v>
       </c>
-      <c r="C15" s="30">
+      <c r="C15" s="25">
         <v>5150</v>
       </c>
-      <c r="D15" s="30">
+      <c r="D15" s="25">
         <v>5305</v>
       </c>
-      <c r="E15" s="30">
+      <c r="E15" s="25">
         <v>5464</v>
       </c>
-      <c r="F15" s="30">
+      <c r="F15" s="25">
         <v>5628</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
-        <v>211</v>
-      </c>
-      <c r="B16" s="31">
+        <v>224</v>
+      </c>
+      <c r="B16" s="32">
         <f>SUM(B15)</f>
         <v>5000</v>
       </c>
-      <c r="C16" s="31">
+      <c r="C16" s="32">
         <f>SUM(C15)</f>
         <v>5150</v>
       </c>
-      <c r="D16" s="31">
+      <c r="D16" s="32">
         <f>SUM(D15)</f>
         <v>5305</v>
       </c>
-      <c r="E16" s="31">
+      <c r="E16" s="32">
         <f>SUM(E15)</f>
         <v>5464</v>
       </c>
-      <c r="F16" s="31">
+      <c r="F16" s="32">
         <f>SUM(F15)</f>
         <v>5628</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="19" t="s">
-        <v>212</v>
-      </c>
-      <c r="B18" s="32">
+        <v>225</v>
+      </c>
+      <c r="B18" s="33">
         <f>SUM(B7,B10,B13,B16)</f>
         <v>221600</v>
       </c>
-      <c r="C18" s="32">
+      <c r="C18" s="33">
         <f>SUM(C7,C10,C13,C16)</f>
         <v>339130</v>
       </c>
-      <c r="D18" s="32">
+      <c r="D18" s="33">
         <f>SUM(D7,D10,D13,D16)</f>
         <v>424882</v>
       </c>
-      <c r="E18" s="32">
+      <c r="E18" s="33">
         <f>SUM(E7,E10,E13,E16)</f>
         <v>495517</v>
       </c>
-      <c r="F18" s="32">
+      <c r="F18" s="33">
         <f>SUM(F7,F10,F13,F16)</f>
         <v>509276</v>
       </c>
@@ -9365,38 +9889,38 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="G3" s="21" t="s">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="H3" s="21" t="s">
-        <v>215</v>
+        <v>228</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>138</v>
-      </c>
-      <c r="C4" s="25">
+        <v>151</v>
+      </c>
+      <c r="C4" s="28">
         <v>1</v>
       </c>
       <c r="D4" s="23">
@@ -9408,21 +9932,21 @@
       <c r="F4" s="24">
         <v>0.0765</v>
       </c>
-      <c r="G4" s="33">
+      <c r="G4" s="34">
         <v>70208</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="C5" s="25">
+        <v>154</v>
+      </c>
+      <c r="C5" s="28">
         <v>1</v>
       </c>
       <c r="D5" s="23">
@@ -9434,21 +9958,21 @@
       <c r="F5" s="24">
         <v>0.0765</v>
       </c>
-      <c r="G5" s="33">
+      <c r="G5" s="34">
         <v>57443</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="C6" s="25">
+        <v>154</v>
+      </c>
+      <c r="C6" s="28">
         <v>0.5</v>
       </c>
       <c r="D6" s="23">
@@ -9460,16 +9984,16 @@
       <c r="F6" s="24">
         <v>0.0765</v>
       </c>
-      <c r="G6" s="33">
+      <c r="G6" s="34">
         <v>15071</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="19" t="s">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="B8" s="19"/>
       <c r="C8" s="19"/>
@@ -9482,78 +10006,78 @@
         <v>7</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D9" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E9" s="21" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F9" s="21" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="B10" s="32">
+        <v>230</v>
+      </c>
+      <c r="B10" s="33">
         <v>118934</v>
       </c>
-      <c r="C10" s="32">
+      <c r="C10" s="33">
         <v>147003</v>
       </c>
-      <c r="D10" s="32">
+      <c r="D10" s="33">
         <v>151413</v>
       </c>
-      <c r="E10" s="32">
+      <c r="E10" s="33">
         <v>155955</v>
       </c>
-      <c r="F10" s="32">
+      <c r="F10" s="33">
         <v>160634</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>218</v>
-      </c>
-      <c r="B11" s="29">
+        <v>231</v>
+      </c>
+      <c r="B11" s="26">
         <v>0.5367065282791817</v>
       </c>
-      <c r="C11" s="29">
+      <c r="C11" s="26">
         <v>0.43347041172111334</v>
       </c>
-      <c r="D11" s="29">
+      <c r="D11" s="26">
         <v>0.35636395851265434</v>
       </c>
-      <c r="E11" s="29">
+      <c r="E11" s="26">
         <v>0.314732109434181</v>
       </c>
-      <c r="F11" s="29">
+      <c r="F11" s="26">
         <v>0.31541616487727187</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>219</v>
-      </c>
-      <c r="B12" s="34">
+        <v>232</v>
+      </c>
+      <c r="B12" s="35">
         <v>4.8</v>
       </c>
-      <c r="C12" s="34">
+      <c r="C12" s="35">
         <v>7.2</v>
       </c>
-      <c r="D12" s="34">
+      <c r="D12" s="35">
         <v>8.8</v>
       </c>
-      <c r="E12" s="34">
+      <c r="E12" s="35">
         <v>10</v>
       </c>
-      <c r="F12" s="34">
+      <c r="F12" s="35">
         <v>10</v>
       </c>
     </row>
@@ -9583,7 +10107,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>220</v>
+        <v>233</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -9596,24 +10120,24 @@
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -9623,52 +10147,52 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>221</v>
-      </c>
-      <c r="B5" s="30">
+        <v>234</v>
+      </c>
+      <c r="B5" s="25">
         <v>6000</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="25">
         <v>9270</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="25">
         <v>11670</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="25">
         <v>13659</v>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="25">
         <v>14069</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>222</v>
-      </c>
-      <c r="B6" s="31">
+        <v>235</v>
+      </c>
+      <c r="B6" s="32">
         <f>SUM(B5:B5)</f>
         <v>6000</v>
       </c>
-      <c r="C6" s="31">
+      <c r="C6" s="32">
         <f>SUM(C5:C5)</f>
         <v>9270</v>
       </c>
-      <c r="D6" s="31">
+      <c r="D6" s="32">
         <f>SUM(D5:D5)</f>
         <v>11670</v>
       </c>
-      <c r="E6" s="31">
+      <c r="E6" s="32">
         <f>SUM(E5:E5)</f>
         <v>13659</v>
       </c>
-      <c r="F6" s="31">
+      <c r="F6" s="32">
         <f>SUM(F5:F5)</f>
         <v>14069</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="19" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="B7" s="19"/>
       <c r="C7" s="19"/>
@@ -9678,52 +10202,52 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>223</v>
-      </c>
-      <c r="B8" s="30">
+        <v>236</v>
+      </c>
+      <c r="B8" s="25">
         <v>3600</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="25">
         <v>5562</v>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="25">
         <v>7002</v>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="25">
         <v>8195</v>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="25">
         <v>8441</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>224</v>
-      </c>
-      <c r="B9" s="31">
+        <v>237</v>
+      </c>
+      <c r="B9" s="32">
         <f>SUM(B8:B8)</f>
         <v>3600</v>
       </c>
-      <c r="C9" s="31">
+      <c r="C9" s="32">
         <f>SUM(C8:C8)</f>
         <v>5562</v>
       </c>
-      <c r="D9" s="31">
+      <c r="D9" s="32">
         <f>SUM(D8:D8)</f>
         <v>7002</v>
       </c>
-      <c r="E9" s="31">
+      <c r="E9" s="32">
         <f>SUM(E8:E8)</f>
         <v>8195</v>
       </c>
-      <c r="F9" s="31">
+      <c r="F9" s="32">
         <f>SUM(F8:F8)</f>
         <v>8441</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="B10" s="19"/>
       <c r="C10" s="19"/>
@@ -9733,92 +10257,92 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>225</v>
-      </c>
-      <c r="B11" s="30">
+        <v>238</v>
+      </c>
+      <c r="B11" s="25">
         <v>30000</v>
       </c>
-      <c r="C11" s="30">
+      <c r="C11" s="25">
         <v>30900</v>
       </c>
-      <c r="D11" s="30">
+      <c r="D11" s="25">
         <v>31827</v>
       </c>
-      <c r="E11" s="30">
+      <c r="E11" s="25">
         <v>32782</v>
       </c>
-      <c r="F11" s="30">
+      <c r="F11" s="25">
         <v>33765</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>226</v>
-      </c>
-      <c r="B12" s="30">
+        <v>239</v>
+      </c>
+      <c r="B12" s="25">
         <v>3600</v>
       </c>
-      <c r="C12" s="30">
+      <c r="C12" s="25">
         <v>3708</v>
       </c>
-      <c r="D12" s="30">
+      <c r="D12" s="25">
         <v>3819</v>
       </c>
-      <c r="E12" s="30">
+      <c r="E12" s="25">
         <v>3934</v>
       </c>
-      <c r="F12" s="30">
+      <c r="F12" s="25">
         <v>4052</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>227</v>
-      </c>
-      <c r="B13" s="30">
+        <v>240</v>
+      </c>
+      <c r="B13" s="25">
         <v>2400</v>
       </c>
-      <c r="C13" s="30">
+      <c r="C13" s="25">
         <v>2472</v>
       </c>
-      <c r="D13" s="30">
+      <c r="D13" s="25">
         <v>2546</v>
       </c>
-      <c r="E13" s="30">
+      <c r="E13" s="25">
         <v>2623</v>
       </c>
-      <c r="F13" s="30">
+      <c r="F13" s="25">
         <v>2701</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>228</v>
-      </c>
-      <c r="B14" s="31">
+        <v>241</v>
+      </c>
+      <c r="B14" s="32">
         <f>SUM(B11:B13)</f>
         <v>36000</v>
       </c>
-      <c r="C14" s="31">
+      <c r="C14" s="32">
         <f>SUM(C11:C13)</f>
         <v>37080</v>
       </c>
-      <c r="D14" s="31">
+      <c r="D14" s="32">
         <f>SUM(D11:D13)</f>
         <v>38192</v>
       </c>
-      <c r="E14" s="31">
+      <c r="E14" s="32">
         <f>SUM(E11:E13)</f>
         <v>39338</v>
       </c>
-      <c r="F14" s="31">
+      <c r="F14" s="32">
         <f>SUM(F11:F13)</f>
         <v>40518</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="B15" s="19"/>
       <c r="C15" s="19"/>
@@ -9828,70 +10352,70 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>229</v>
-      </c>
-      <c r="B16" s="30">
+        <v>242</v>
+      </c>
+      <c r="B16" s="25">
         <v>3000</v>
       </c>
-      <c r="C16" s="30">
+      <c r="C16" s="25">
         <v>3090</v>
       </c>
-      <c r="D16" s="30">
+      <c r="D16" s="25">
         <v>3183</v>
       </c>
-      <c r="E16" s="30">
+      <c r="E16" s="25">
         <v>3278</v>
       </c>
-      <c r="F16" s="30">
+      <c r="F16" s="25">
         <v>3377</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>230</v>
-      </c>
-      <c r="B17" s="31">
+        <v>243</v>
+      </c>
+      <c r="B17" s="32">
         <f>SUM(B16:B16)</f>
         <v>3000</v>
       </c>
-      <c r="C17" s="31">
+      <c r="C17" s="32">
         <f>SUM(C16:C16)</f>
         <v>3090</v>
       </c>
-      <c r="D17" s="31">
+      <c r="D17" s="32">
         <f>SUM(D16:D16)</f>
         <v>3183</v>
       </c>
-      <c r="E17" s="31">
+      <c r="E17" s="32">
         <f>SUM(E16:E16)</f>
         <v>3278</v>
       </c>
-      <c r="F17" s="31">
+      <c r="F17" s="32">
         <f>SUM(F16:F16)</f>
         <v>3377</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
-        <v>231</v>
-      </c>
-      <c r="B19" s="32">
+        <v>244</v>
+      </c>
+      <c r="B19" s="33">
         <f>B6+B9+B14+B17</f>
         <v>48600</v>
       </c>
-      <c r="C19" s="32">
+      <c r="C19" s="33">
         <f>C6+C9+C14+C17</f>
         <v>55002</v>
       </c>
-      <c r="D19" s="32">
+      <c r="D19" s="33">
         <f>D6+D9+D14+D17</f>
         <v>60047</v>
       </c>
-      <c r="E19" s="32">
+      <c r="E19" s="33">
         <f>E6+E9+E14+E17</f>
         <v>64471</v>
       </c>
-      <c r="F19" s="32">
+      <c r="F19" s="33">
         <f>F6+F9+F14+F17</f>
         <v>66405</v>
       </c>
@@ -9923,7 +10447,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>232</v>
+        <v>245</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -9933,30 +10457,30 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>233</v>
+        <v>246</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="C4" s="23">
         <v>30000</v>
@@ -9967,23 +10491,23 @@
       <c r="E4" s="22">
         <v>5</v>
       </c>
-      <c r="F4" s="33">
+      <c r="F4" s="34">
         <v>6960</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>234</v>
-      </c>
-      <c r="F6" s="32">
+        <v>247</v>
+      </c>
+      <c r="F6" s="33">
         <v>6960</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>235</v>
-      </c>
-      <c r="F7" s="31">
+        <v>248</v>
+      </c>
+      <c r="F7" s="32">
         <v>30000</v>
       </c>
     </row>
